--- a/weekly_temp/patents_量子软件与算法.xlsx
+++ b/weekly_temp/patents_量子软件与算法.xlsx
@@ -456,17 +456,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>量子计算控制装置、量子计算机及量子计算控制方法</t>
+          <t>学习装置、数据处理装置、参数生成装置、学习方法、数据处理方法和参数生成方法</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>独立行政法人科学技术振兴机构</t>
+          <t>索尼集团公司</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>中村泰信 | 田渊丰 | 玉手修平</t>
+          <t>INAISHI, DAISUKE | ARAI, HIROAKI | HIRAI, YUMA | KOSAKA, JUNICHI | KANAO, RINNA</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -476,184 +476,182 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>量子计算控制装置具备控制信号生成部和量子比特模块。量子比特模块具备观测部、量子比特基板部、控制电路部、观测电路部以及信号处理电路部。多个量子比特分组为由各量子比特彼此的位置关系相同的多个量子比特构成的多个组而配置在量子比特基板部上。控制信号生成部生成控制信号和命令信号，控制信号用于执行一个以上的种类的空间上均匀的第一操作及以比一个以上的种类的第一操作低的频度来进行的空间上不均匀的第二操作，命令信号用于使控制电路部执行第一操作及第二操作的控制，该第一操作及第二操作是针对量子比特基板部上的量子比特的操作。控制电路部将控制信号分支到组，根据命令信号，对控制信号向量子比特基板部上的各量子比特的送出进行控制。观测电路部观测接受了第一操作或第二操作的各量子比特的状态。信号处理电路部向观测部发送各量子比特的观测信号。</t>
+          <t>在学习装置(10)中,第一评估单元(14)对多个图像数据进行定量评估,从而获取针对多个图像数据中的每一个的多个第一评估结果;教师数据生成单元(15)基于多个第一评估结果,从具有彼此不同值的多个第一参数中选择第二参数,并生成包括所选第二参数的第一组教师数据;第一机器学习单元(17)使用第一组教师数据进行机器学习,从而生成输出用于处理处理目标的图像数据的第三参数的学习模型。</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://analytics.zhihuiya.com/patent-view/abst?patentId=efec951d-1740-473f-842d-97180ce3a76d&amp;shareId=1FE8B6DF-4B44-81FE-235C-3B3890D5E284&amp;from=EXPORT&amp;signature=cWStYX30VcRxj2P%2BjMY8Zcter538VTu%2BbtjG7vto470%3D&amp;expire=94608000&amp;date=20260529T004546Z&amp;version=1.0</t>
+          <t>https://analytics.zhihuiya.com/patent-view/abst?patentId=09b602ca-7cd6-46b9-89a4-4e1187e8767c&amp;shareId=1FE8B6DF-4B44-81FE-235C-3B3890D5E284&amp;from=EXPORT&amp;signature=Cngt8rv7tt158dYJYry8%2BZbNvBX8N1TGHCAHUIPW%2Fyw%3D&amp;expire=94608000&amp;date=20260529T004546Z&amp;version=1.0</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>原子的电子态分离器、原子干涉仪、原子跃迁频率测量装置、原子振荡器、光晶格钟、量子计算机及原子的电子态叠加态的生成方法</t>
+          <t>量子计算系统中的参量放大</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>国立大学法人东京大学</t>
+          <t>RIGETTI &amp; CO INC</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>香取秀俊</t>
+          <t>SELVANAYAGAM,, MICHAEL KARUNENDRA | RAMACHANDRAN,, GANESH | MOHAN,, YUVRAJ | SHARAC,, NICHOLAS WARREN | FENG,, DENNIS CHEN | VAHIDPOUR,, MEHRNOOSH</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>授权专利</t>
+          <t>公开专利</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>本发明的原子的电子态分离器(1)包括：原子供给部(11)、原子移动路径(12)、探测激光光源(13)和磁场生成部(M)。原子供给部(11)供给以一定速度在原子移动路径(12)中移动的原子。探测激光光源(13)向原子移动路径(12)内供给与原子移动路径(12)同轴地在与原子的运动方向相反或相同的方向上传播的探测激光。磁场生成部(M)通过在原子移动路径(12)中生成与原子移动路径(12)正交的磁场并进行与容许电偶极子跃迁的电子态的波函数混合，能够进行基于在时间和空间上同样的探测激光的时钟跃迁的脉冲激发。或者，磁屏蔽件通过屏蔽在原子移动路径(12)中施加的磁场并在空间上改变塞曼频移，从而能够通过在时间和空间上同样的探测激光对时钟跃迁进行脉冲激发。其结果，能够连续地进行原子跃迁的分光和探测激光的频率控制，提高原子钟的稳定度。</t>
+          <t>一般来说,参量放大是在量子计算系统中实现的。在某些情况下,行波参量放大器(TWPA)包含多个串联的约瑟夫森结。这些约瑟夫森结包括一个第一约瑟夫森结,该第一约瑟夫森结包括位于衬底表面上的第一超导电极、与第一超导电极重叠的第二超导电极,以及夹在第一和第二超导电极重叠部分之间的势垒。该势垒在衬底表面上形成一个锥形区域。</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://analytics.zhihuiya.com/patent-view/abst?patentId=826fc8c9-43e7-46de-ba8a-7944a1978dc4&amp;shareId=1FE8B6DF-4B44-81FE-235C-3B3890D5E284&amp;from=EXPORT&amp;signature=LlykcgPkjh3vLSNIh6JaxjqICxUxQMbBk6mblb38Uwg%3D&amp;expire=94608000&amp;date=20260529T004546Z&amp;version=1.0</t>
+          <t>https://analytics.zhihuiya.com/patent-view/abst?patentId=5a6b90a4-a56f-4568-9561-e3f877eac10f&amp;shareId=1FE8B6DF-4B44-81FE-235C-3B3890D5E284&amp;from=EXPORT&amp;signature=oDm5LSn6jC86Ao1xLgF%2BCW%2BmwUGg0v9UbX26H7BQkTI%3D&amp;expire=94608000&amp;date=20260529T004546Z&amp;version=1.0</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>基于FPGA的蒙特卡罗路径积分-模拟量子退火方法及系统</t>
+          <t>利用人工智能解决特定领域问题</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>西安电子科技大学</t>
+          <t>人工天才公司</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>朱畅华 | 李帅威 | 何先灯 | 魏建涛 | 权东晓 | 易运晖 | 赵楠 | 陈南</t>
+          <t>BURCHARD, PAUL</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>授权专利</t>
+          <t>公开专利</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>本发明公开了一种基于FPGA实现的蒙特卡罗路径积分‑模拟量子退火方法，主要解决现有蒙特卡罗路径积分‑模拟量子退火算法在CPU上运行时间效率低的问题，其实现方案包括:在Bram空间初始化原始矩阵；FPGA产生随机数以对原始矩阵进行随机操作得到新矩阵；并行计算新矩阵和原始矩阵势能项差值、动能项差值和哈密顿量差值；判断是否更新原始矩阵；选择执行更新操作后原始矩阵中势能项最小的矩阵作为当前的最优方案解；更新耦合系数不断进行迭代直到设定的迭代次数，得到最优解即为最终的最优路径。本发明大幅提升了运行的时间效率，相对于传统的蒙特卡罗路径积分‑模拟量子退火算法运行时间提高了79倍，可用于实时性要求高场景的无人机路由规划。</t>
+          <t>本文描述了利用人工智能为特定领域问题提供可解释解决方案的新方法。计算单元识别特定领域问题,例如生物学问题。计算单元确定一个初始特征子集,该子集包含该问题可观察特征的各种特征。计算单元优化初始特征子集,以提高该子集生成问题解决方案的准确性。计算单元基于优化后的子集训练一个或多个预测人工智能模型,以输出该问题的解决方案。随后,计算单元利用训练后的预测模型输出一个或多个其他特定领域问题的解决方案。计算单元还可以通过输出预测模型执行的步骤的表示来为特定领域的问题提供可解释的解决方案。</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://analytics.zhihuiya.com/patent-view/abst?patentId=4995bc0f-40ae-45ff-a154-7460d307f8a1&amp;shareId=1FE8B6DF-4B44-81FE-235C-3B3890D5E284&amp;from=EXPORT&amp;signature=mw%2F8XzKpXOlI5GwRkITNxI8qXk7gfaPvM1rU8BWWW%2BY%3D&amp;expire=94608000&amp;date=20260529T004546Z&amp;version=1.0</t>
+          <t>https://analytics.zhihuiya.com/patent-view/abst?patentId=ed3db125-1edd-46c4-8bec-b6f6711e683e&amp;shareId=1FE8B6DF-4B44-81FE-235C-3B3890D5E284&amp;from=EXPORT&amp;signature=%2Bp73R2mjhqlXvbjBOiG8LTALKPBFpupReNchfjFm2Rc%3D&amp;expire=94608000&amp;date=20260529T004546Z&amp;version=1.0</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>用于量子计算测控的集成滤波放大装置</t>
+          <t>利用量子纠缠的大型语言模型</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>相干(北京)科技有限公司</t>
+          <t>万事达卡国际股份有限公司</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>赵剑琴 | 邢磊 | 田建强 | 贺玉龙 | 曾祥洪</t>
+          <t>MALEKI, MEHRDAD | KOTHALE, NITISH</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>授权专利</t>
+          <t>公开专利</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>本申请涉及一种用于量子计算测控的集成滤波放大装置，包括：装置壳体、电路板、前端衰减组件、前端带通滤波组件、微波放大组件、后端衰减组件和后端带通滤波组件，前端带通滤波组件、前端衰减组件、微波放大组件、后端衰减组件和后端带通滤波组件，依次连接设置在所述电路板上，且均集成在装置壳体内，通过集成带通滤波器、衰减器和微波放大器的微波前端模块，极大降低了外部线路复杂性，且该集成前端模块体积小，可直接集成到电子学设备中，使得测控脉冲从电子学设备中发生后可直接接入稀释制冷机内，极大简化了外部接线，提升了系统可靠性。</t>
+          <t>一种利用量子系统存储训练模型的方法 400 包括:接收 404 至少一个代表训练模型的参数集,该至少一个参数集包含一个或多个参数;基于该至少一个参数集生成 406 至少一个纠缠态;以及将该至少一个纠缠态存储 408 于量子系统中。通过测量该纠缠态,可以确定该至少一个参数集中的至少一个参数。</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://analytics.zhihuiya.com/patent-view/abst?patentId=02fd591a-9387-4d8e-abef-42688565ec39&amp;shareId=1FE8B6DF-4B44-81FE-235C-3B3890D5E284&amp;from=EXPORT&amp;signature=Y4mWB4Qgq0ZN0ZF5c9ezw5g6r96S%2FlAdiLwncSSBkfo%3D&amp;expire=94608000&amp;date=20260529T004546Z&amp;version=1.0</t>
+          <t>https://analytics.zhihuiya.com/patent-view/abst?patentId=7042cefd-dbf9-4dc0-9986-4066c797dacb&amp;shareId=1FE8B6DF-4B44-81FE-235C-3B3890D5E284&amp;from=EXPORT&amp;signature=hooi9d145BlHbvp5hiMpYPi36uudoDuUhSK4%2BH%2B3ZfU%3D&amp;expire=94608000&amp;date=20260529T004546Z&amp;version=1.0</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>量子自旋液体中的拓扑量子比特</t>
+          <t>作业调度程序、作业调度方法和信息处理设备</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>哈佛大学校长及研究员协会 | 麻省理工学院</t>
+          <t>富士通株式会社</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>ルーキン,ミハイル,ディー. | ヴュレティック,ヴラダン | グライナー,マルクス | ベレセン,ルーベン | ビシュワナート,アシュビン | コントレラス,アレキサンダー キースリング | レビン,ハリー,ジェイ | セメギニ,ジュリア | ワン,タウト タオタオ | オムラン,アーメド | ブルブスタイン,ドレフ | エバディ,セパー</t>
+          <t>NODA, KUNIHIRO</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>授权专利</t>
+          <t>公开专利</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>在一个实施例中,提供了一种装置,该装置包括二维粒子阵列,每个粒子包含: 
- [公式 1] 
- TIFF2023552091000460.tif8150;每个粒子具有第一态和激发态;属于红宝石晶格至少三个晶胞的每个粒子具有足够的阻塞半径,当处于激发态时,可以阻止红宝石晶格中至少六个最近邻粒子从其第一态跃迁到其激发态,并且该阵列具有至少一个外边缘,配置为处于第一边界条件。</t>
+          <t>量子计算任务得以高效执行。信息处理装置(10)将指示执行量子计算的任务(3a,3b)放入第一队列(1)。信息处理装置(10)将第一队列(1)中的每个任务(4a至4d)的量子计算过程转换为量子计算机(6)可执行的指令序列。信息处理装置(10)将转换完成的任务(4a至4d)放入第二队列(2)。信息处理装置(10)根据预定标准,从第二队列(2)的队首依次选择每个任务(5a至5d),确定用于执行该任务的量子比特以及是否立即执行该任务。信息处理装置(10)在确定任务需要立即执行后,指示量子计算机(6)执行该任务。</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://analytics.zhihuiya.com/patent-view/abst?patentId=16e4dc1c-3013-41eb-91c4-0e2bc35596d1&amp;shareId=1FE8B6DF-4B44-81FE-235C-3B3890D5E284&amp;from=EXPORT&amp;signature=sj1sEqHYPP7crG2lXPyE2kDFi9zchD9Go8aJv4DyFJ0%3D&amp;expire=94608000&amp;date=20260529T004546Z&amp;version=1.0</t>
+          <t>https://analytics.zhihuiya.com/patent-view/abst?patentId=2c1a0b60-a7e0-46a1-af8d-2b1090e2e607&amp;shareId=1FE8B6DF-4B44-81FE-235C-3B3890D5E284&amp;from=EXPORT&amp;signature=2MnEtmUDx8zJxGQZoQLzRsmJlcPLfXpNAYfboFFuuRM%3D&amp;expire=94608000&amp;date=20260529T004546Z&amp;version=1.0</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>转译过程中的手动量子比特映射</t>
+          <t>量子计算控制装置、量子计算机及量子计算控制方法</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>戴尔产品有限公司</t>
+          <t>独立行政法人科学技术振兴机构</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>HEALY, BRENDAN BURNS | TEIXEIRA DE ABREU PINHO, RÔMULO | FONG, VICTOR</t>
+          <t>中村泰信 | 田渊丰 | 玉手修平</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -668,29 +666,29 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>一种方法包括:获取待映射到量子电路相应虚拟量子比特的物理量子比特的误差信息;基于这些误差信息对物理量子比特进行采样;将虚拟量子比特映射到采样得到的物理量子比特;以及对采样得到的物理量子比特执行一次量子电路。这些操作可以重复执行n次,直到获得可接受的量子电路执行结果。</t>
+          <t>量子计算控制装置具备控制信号生成部和量子比特模块。量子比特模块具备观测部、量子比特基板部、控制电路部、观测电路部以及信号处理电路部。多个量子比特分组为由各量子比特彼此的位置关系相同的多个量子比特构成的多个组而配置在量子比特基板部上。控制信号生成部生成控制信号和命令信号，控制信号用于执行一个以上的种类的空间上均匀的第一操作及以比一个以上的种类的第一操作低的频度来进行的空间上不均匀的第二操作，命令信号用于使控制电路部执行第一操作及第二操作的控制，该第一操作及第二操作是针对量子比特基板部上的量子比特的操作。控制电路部将控制信号分支到组，根据命令信号，对控制信号向量子比特基板部上的各量子比特的送出进行控制。观测电路部观测接受了第一操作或第二操作的各量子比特的状态。信号处理电路部向观测部发送各量子比特的观测信号。</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://analytics.zhihuiya.com/patent-view/abst?patentId=3d214994-e647-41da-b11b-9b048d2a7d08&amp;shareId=1FE8B6DF-4B44-81FE-235C-3B3890D5E284&amp;from=EXPORT&amp;signature=2B9SaHQRQETEbhhaTk%2FXM877NJgEZDaUpN%2FMi7BHWaQ%3D&amp;expire=94608000&amp;date=20260529T004546Z&amp;version=1.0</t>
+          <t>https://analytics.zhihuiya.com/patent-view/abst?patentId=efec951d-1740-473f-842d-97180ce3a76d&amp;shareId=1FE8B6DF-4B44-81FE-235C-3B3890D5E284&amp;from=EXPORT&amp;signature=cWStYX30VcRxj2P%2BjMY8Zcter538VTu%2BbtjG7vto470%3D&amp;expire=94608000&amp;date=20260529T004546Z&amp;version=1.0</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>结合量子计算、博弈论优化及相关方法的射频信号分类装置</t>
+          <t>原子的电子态分离器、原子干涉仪、原子跃迁频率测量装置、原子振荡器、光晶格钟、量子计算机及原子的电子态叠加态的生成方法</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>伊格尔科技有限责任公司</t>
+          <t>国立大学法人东京大学</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>LAU, CHAD | RAHMES, MARK D. | CHESTER, DAVID B. | GARRETT, MICHAEL C.</t>
+          <t>香取秀俊</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -705,29 +703,29 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>一种射频(RF)信号分类装置可包括:射频接收器,用于接收射频信号;量子计算电路,用于执行量子子集求和;以及处理器。该处理器可配置为:为多个不同的深度学习模型生成博弈论奖励矩阵;与量子计算电路协作,对该博弈论奖励矩阵执行量子子集求和;基于该量子子集求和结果,从多个深度学习模型中选择一个;以及使用所选的深度学习模型处理射频信号,以进行射频信号分类。</t>
+          <t>本发明的原子的电子态分离器(1)包括：原子供给部(11)、原子移动路径(12)、探测激光光源(13)和磁场生成部(M)。原子供给部(11)供给以一定速度在原子移动路径(12)中移动的原子。探测激光光源(13)向原子移动路径(12)内供给与原子移动路径(12)同轴地在与原子的运动方向相反或相同的方向上传播的探测激光。磁场生成部(M)通过在原子移动路径(12)中生成与原子移动路径(12)正交的磁场并进行与容许电偶极子跃迁的电子态的波函数混合，能够进行基于在时间和空间上同样的探测激光的时钟跃迁的脉冲激发。或者，磁屏蔽件通过屏蔽在原子移动路径(12)中施加的磁场并在空间上改变塞曼频移，从而能够通过在时间和空间上同样的探测激光对时钟跃迁进行脉冲激发。其结果，能够连续地进行原子跃迁的分光和探测激光的频率控制，提高原子钟的稳定度。</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://analytics.zhihuiya.com/patent-view/abst?patentId=494c5522-0862-40b4-9e48-8eede396c76b&amp;shareId=1FE8B6DF-4B44-81FE-235C-3B3890D5E284&amp;from=EXPORT&amp;signature=gFV1pUFHsr%2BTO14GvyYlrExaQaex6lQray4estnB0Jc%3D&amp;expire=94608000&amp;date=20260529T004546Z&amp;version=1.0</t>
+          <t>https://analytics.zhihuiya.com/patent-view/abst?patentId=826fc8c9-43e7-46de-ba8a-7944a1978dc4&amp;shareId=1FE8B6DF-4B44-81FE-235C-3B3890D5E284&amp;from=EXPORT&amp;signature=LlykcgPkjh3vLSNIh6JaxjqICxUxQMbBk6mblb38Uwg%3D&amp;expire=94608000&amp;date=20260529T004546Z&amp;version=1.0</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>量子比特注册表命名空间</t>
+          <t>基于FPGA的蒙特卡罗路径积分-模拟量子退火方法及系统</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>红帽公司</t>
+          <t>西安电子科技大学</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>GRIFFIN, LEIGH | COADY, STEPHEN</t>
+          <t>朱畅华 | 李帅威 | 何先灯 | 魏建涛 | 权东晓 | 易运晖 | 赵楠 | 陈南</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -742,12 +740,12 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>量子计算设备从对应于第一量子过程的第一量子指令文件(QIF)中获取第一量子过程所需的量子比特数量。该量子计算设备在包含多个量子比特注册表项的量子比特注册表中创建第一命名空间,每个注册表项对应于多个量子比特中的一个量子比特,该第一命名空间指向多个量子比特中的第一子集,该第一子集包含至少第一量子过程所需的量子比特数量。该量子计算设备将第一命名空间的标识符插入到第一QIF中。当第一QIF执行时,该量子计算设备使量子比特注册表向第一量子过程提供对第一命名空间的访问权限。</t>
+          <t>本发明公开了一种基于FPGA实现的蒙特卡罗路径积分‑模拟量子退火方法，主要解决现有蒙特卡罗路径积分‑模拟量子退火算法在CPU上运行时间效率低的问题，其实现方案包括:在Bram空间初始化原始矩阵；FPGA产生随机数以对原始矩阵进行随机操作得到新矩阵；并行计算新矩阵和原始矩阵势能项差值、动能项差值和哈密顿量差值；判断是否更新原始矩阵；选择执行更新操作后原始矩阵中势能项最小的矩阵作为当前的最优方案解；更新耦合系数不断进行迭代直到设定的迭代次数，得到最优解即为最终的最优路径。本发明大幅提升了运行的时间效率，相对于传统的蒙特卡罗路径积分‑模拟量子退火算法运行时间提高了79倍，可用于实时性要求高场景的无人机路由规划。</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://analytics.zhihuiya.com/patent-view/abst?patentId=6e9dd29e-9742-4463-ad18-2eb4df554e2f&amp;shareId=1FE8B6DF-4B44-81FE-235C-3B3890D5E284&amp;from=EXPORT&amp;signature=CmlCg9NACI2sRKU5A8xtBPEjkYDj8rCk0aTVvbWZ%2Fk4%3D&amp;expire=94608000&amp;date=20260529T004546Z&amp;version=1.0</t>
+          <t>https://analytics.zhihuiya.com/patent-view/abst?patentId=4995bc0f-40ae-45ff-a154-7460d307f8a1&amp;shareId=1FE8B6DF-4B44-81FE-235C-3B3890D5E284&amp;from=EXPORT&amp;signature=mw%2F8XzKpXOlI5GwRkITNxI8qXk7gfaPvM1rU8BWWW%2BY%3D&amp;expire=94608000&amp;date=20260529T004546Z&amp;version=1.0</t>
         </is>
       </c>
     </row>

--- a/weekly_temp/patents_量子软件与算法.xlsx
+++ b/weekly_temp/patents_量子软件与算法.xlsx
@@ -456,54 +456,54 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>学习装置、数据处理装置、参数生成装置、学习方法、数据处理方法和参数生成方法</t>
+          <t>基于量子干涉采样的组合优化</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>索尼集团公司</t>
+          <t>谷歌有限责任公司</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>INAISHI, DAISUKE | ARAI, HIROAKI | HIRAI, YUMA | KOSAKA, JUNICHI | KANAO, RINNA</t>
+          <t>JORDAN, STEPHEN, PAUL</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>授权专利</t>
+          <t>公开专利</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>在学习装置(10)中,第一评估单元(14)对多个图像数据进行定量评估,从而获取针对多个图像数据中的每一个的多个第一评估结果;教师数据生成单元(15)基于多个第一评估结果,从具有彼此不同值的多个第一参数中选择第二参数,并生成包括所选第二参数的第一组教师数据;第一机器学习单元(17)使用第一组教师数据进行机器学习,从而生成输出用于处理处理目标的图像数据的第三参数的学习模型。</t>
+          <t>本发明公开了一种用于优化包含一组自由度 (DOF) 和一组针对该 DOF 的约束的系统的方法。每个约束与该 DOF 集的一个子集相关联。该方法包括确定第一个多项式函数。量子计算系统 (QCS) 的一组量子比特在第一量子态下准备。在第一量子态下准备该组量子比特后,QCS 对该组量子比特执行一组幺正运算。在该组量子比特执行该组幺正运算后,QCS 通过对该组量子比特中的每个量子比特执行第一次测量操作来生成第一组可观测量。基于第一组可观测量确定一组值。</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://analytics.zhihuiya.com/patent-view/abst?patentId=09b602ca-7cd6-46b9-89a4-4e1187e8767c&amp;shareId=1FE8B6DF-4B44-81FE-235C-3B3890D5E284&amp;from=EXPORT&amp;signature=Cngt8rv7tt158dYJYry8%2BZbNvBX8N1TGHCAHUIPW%2Fyw%3D&amp;expire=94608000&amp;date=20260529T004546Z&amp;version=1.0</t>
+          <t>https://analytics.zhihuiya.com/patent-view/abst?patentId=beb237b0-424b-4221-a72c-bd637552d779&amp;shareId=1B475C3G-7GDG-8976-149D-791913G50906&amp;from=EXPORT&amp;signature=Fc9PUiPsEY%2BdIF3wHPUrxnJZNZBVa%2BvhLOLvvonDkE8%3D&amp;expire=94608000&amp;date=20260605T004519Z&amp;version=1.0</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>量子计算系统中的参量放大</t>
+          <t>通过量子计算和量子通信的分布式机器学习</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>RIGETTI &amp; CO INC</t>
+          <t>谷歌有限责任公司</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>SELVANAYAGAM,, MICHAEL KARUNENDRA | RAMACHANDRAN,, GANESH | MOHAN,, YUVRAJ | SHARAC,, NICHOLAS WARREN | FENG,, DENNIS CHEN | VAHIDPOUR,, MEHRNOOSH</t>
+          <t>GILBOA, DAR | MCCLEAN, JARROD RYAN</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -513,145 +513,145 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>一般来说,参量放大是在量子计算系统中实现的。在某些情况下,行波参量放大器(TWPA)包含多个串联的约瑟夫森结。这些约瑟夫森结包括一个第一约瑟夫森结,该第一约瑟夫森结包括位于衬底表面上的第一超导电极、与第一超导电极重叠的第二超导电极,以及夹在第一和第二超导电极重叠部分之间的势垒。该势垒在衬底表面上形成一个锥形区域。</t>
+          <t>一个实施例包括一种方法,该方法包括在具有多个量子节点和量子通信网络的分布式量子计算系统 (DQCS) 上接收第一输入。基于第一输入和一个模型,在多个节点中的第一个量子节点上执行第一量子计算。第一量子计算的输出通过量子通信网络传输到多个量子节点中的第二个量子节点。基于第一量子计算的输出和在第二量子节点上实施的量子断层扫描算法,计算出分布式计算的结果。</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://analytics.zhihuiya.com/patent-view/abst?patentId=5a6b90a4-a56f-4568-9561-e3f877eac10f&amp;shareId=1FE8B6DF-4B44-81FE-235C-3B3890D5E284&amp;from=EXPORT&amp;signature=oDm5LSn6jC86Ao1xLgF%2BCW%2BmwUGg0v9UbX26H7BQkTI%3D&amp;expire=94608000&amp;date=20260529T004546Z&amp;version=1.0</t>
+          <t>https://analytics.zhihuiya.com/patent-view/abst?patentId=41983739-7b03-4a29-8a94-d42bd288f1c3&amp;shareId=1B475C3G-7GDG-8976-149D-791913G50906&amp;from=EXPORT&amp;signature=x2zwu5O68qAiOi1FfzjLIcHII840OPb%2BA%2BBRigla0v4%3D&amp;expire=94608000&amp;date=20260605T004519Z&amp;version=1.0</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>利用人工智能解决特定领域问题</t>
+          <t>光纤型激光功率量子控制装置、方法、激光发射设备</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>人工天才公司</t>
+          <t>北京无线电计量测试研究所</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>BURCHARD, PAUL</t>
+          <t>纪仟仟 | 薛潇博 | 韩蕾 | 申彤 | 苏亚北 | 张升康 | 葛军</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>公开专利</t>
+          <t>授权专利</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>本文描述了利用人工智能为特定领域问题提供可解释解决方案的新方法。计算单元识别特定领域问题,例如生物学问题。计算单元确定一个初始特征子集,该子集包含该问题可观察特征的各种特征。计算单元优化初始特征子集,以提高该子集生成问题解决方案的准确性。计算单元基于优化后的子集训练一个或多个预测人工智能模型,以输出该问题的解决方案。随后,计算单元利用训练后的预测模型输出一个或多个其他特定领域问题的解决方案。计算单元还可以通过输出预测模型执行的步骤的表示来为特定领域的问题提供可解释的解决方案。</t>
+          <t>本说明书公开了一种光纤型激光功率量子控制装置、方法、激光发射设备，以提高激光功率的抗干扰能力和稳定度。本发明装置包括：第一支路，配置为对激光器输出的激光，经过声光调制器输出0级衍射光，经光纤隔离器后输出待稳功率激光；第二支路为反馈调节支路，将第一支路中的待稳功率激光作为监测信号，导入原子钟使原子钟的输出频率随之改变，基于该输出频率与给定输出频率之间的偏差，通过反馈控制方法对第一支路中激光偏振态进行调整，以稳定输出激光的功率。本发明中，使用全光纤结构的量子控制装置具有结构简单、体积小巧、成本低、重量轻、实验装置难度低、免于调试空间光路、不易受外界杂散光影响的优势，并且提高了激光功率稳定度。</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://analytics.zhihuiya.com/patent-view/abst?patentId=ed3db125-1edd-46c4-8bec-b6f6711e683e&amp;shareId=1FE8B6DF-4B44-81FE-235C-3B3890D5E284&amp;from=EXPORT&amp;signature=%2Bp73R2mjhqlXvbjBOiG8LTALKPBFpupReNchfjFm2Rc%3D&amp;expire=94608000&amp;date=20260529T004546Z&amp;version=1.0</t>
+          <t>https://analytics.zhihuiya.com/patent-view/abst?patentId=819b526b-053e-44fe-abb9-bc58efecb2c1&amp;shareId=1B475C3G-7GDG-8976-149D-791913G50906&amp;from=EXPORT&amp;signature=eDjSYHnwujwUnfnLRX7a6lcTR7W36aTMxSFLUA%2BMZtU%3D&amp;expire=94608000&amp;date=20260605T004519Z&amp;version=1.0</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>利用量子纠缠的大型语言模型</t>
+          <t>偏振控制的激光功率量子稳定装置、方法、激光发射设备</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>万事达卡国际股份有限公司</t>
+          <t>北京无线电计量测试研究所</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>MALEKI, MEHRDAD | KOTHALE, NITISH</t>
+          <t>纪仟仟 | 薛潇博 | 韩蕾 | 申彤 | 苏亚北 | 张升康 | 葛军</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>公开专利</t>
+          <t>授权专利</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>一种利用量子系统存储训练模型的方法 400 包括:接收 404 至少一个代表训练模型的参数集,该至少一个参数集包含一个或多个参数;基于该至少一个参数集生成 406 至少一个纠缠态;以及将该至少一个纠缠态存储 408 于量子系统中。通过测量该纠缠态,可以确定该至少一个参数集中的至少一个参数。</t>
+          <t>本说明书公开了一种偏振控制的激光功率量子稳定装置、方法、激光发射设备，以提高激光功率的稳定性。本发明装置包括：激光功率调整单元，配置为对激光器输出的线偏振光，采用偏振控制器进行激光偏振态的调整，并经保偏传输后输出待稳功率激光；反馈控制单元，配置为以待稳功率激光作为监测对象，将其导入原子钟，使原子钟输出频率随之改变，基于该输出频率与给定输出频率之间的偏差，通过反馈控制方法对激光功率调整单元中激光偏振态进行调整，以稳定输出激光的功率。本发明抗环境干扰能力强、减小了传统方法里激光偏振变化对功率稳定的影响，提高了系统稳定功率微小变化的灵敏度和响应能力，更加精准的进行稳定激光功率的控制。</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://analytics.zhihuiya.com/patent-view/abst?patentId=7042cefd-dbf9-4dc0-9986-4066c797dacb&amp;shareId=1FE8B6DF-4B44-81FE-235C-3B3890D5E284&amp;from=EXPORT&amp;signature=hooi9d145BlHbvp5hiMpYPi36uudoDuUhSK4%2BH%2B3ZfU%3D&amp;expire=94608000&amp;date=20260529T004546Z&amp;version=1.0</t>
+          <t>https://analytics.zhihuiya.com/patent-view/abst?patentId=676a11df-8175-4c2e-a0bf-56f414fb96a8&amp;shareId=1B475C3G-7GDG-8976-149D-791913G50906&amp;from=EXPORT&amp;signature=VSiYnCmNha%2BQaeQPLSGbuT%2FMEBPmMphs47whZ4h3atw%3D&amp;expire=94608000&amp;date=20260605T004519Z&amp;version=1.0</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>作业调度程序、作业调度方法和信息处理设备</t>
+          <t>太赫兹光谱量子弱测量方法、系统及应用</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>富士通株式会社</t>
+          <t>中国科学院深圳先进技术研究院</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>NODA, KUNIHIRO</t>
+          <t>常天英 | 崔洪亮 | 路星星 | 魏东山 | 汪岳峰</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>公开专利</t>
+          <t>授权专利</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>量子计算任务得以高效执行。信息处理装置(10)将指示执行量子计算的任务(3a,3b)放入第一队列(1)。信息处理装置(10)将第一队列(1)中的每个任务(4a至4d)的量子计算过程转换为量子计算机(6)可执行的指令序列。信息处理装置(10)将转换完成的任务(4a至4d)放入第二队列(2)。信息处理装置(10)根据预定标准,从第二队列(2)的队首依次选择每个任务(5a至5d),确定用于执行该任务的量子比特以及是否立即执行该任务。信息处理装置(10)在确定任务需要立即执行后,指示量子计算机(6)执行该任务。</t>
+          <t>本发明提供了太赫兹光谱量子弱测量方法、系统及应用，属于太赫兹技术领域，该太赫兹光谱量子弱测量方法应用于太赫兹光谱量子弱测量系统，所述系统包括第一偏振片、第二偏振片、太赫兹时域光谱单元、发射端、探测端及样品载体，本发明提出的基于量子弱值放大效应的太赫兹量子弱测量方法及系统，能够突破目前太赫兹技术的痕量检测极限。本发明通过选定一个太赫兹偏振状态(前选态)，被测量的微小变化对其产生一种“微”扰动，再用强测量将被扰动系统态投影到后选态上，进而建立太赫兹量子弱测量体系；大多手性药物在太赫兹波段具有共振吸收性，有益于利用手性分子的旋光度微变化作为弱耦合作用，实现手性药物的高灵敏构象识别。</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://analytics.zhihuiya.com/patent-view/abst?patentId=2c1a0b60-a7e0-46a1-af8d-2b1090e2e607&amp;shareId=1FE8B6DF-4B44-81FE-235C-3B3890D5E284&amp;from=EXPORT&amp;signature=2MnEtmUDx8zJxGQZoQLzRsmJlcPLfXpNAYfboFFuuRM%3D&amp;expire=94608000&amp;date=20260529T004546Z&amp;version=1.0</t>
+          <t>https://analytics.zhihuiya.com/patent-view/abst?patentId=c9746448-bedc-4316-b621-fe01a87980db&amp;shareId=1B475C3G-7GDG-8976-149D-791913G50906&amp;from=EXPORT&amp;signature=wi1MMHbFVv7qi%2BmluFU5HXTRO59DnQ5Cn1nbNzzY1ak%3D&amp;expire=94608000&amp;date=20260605T004519Z&amp;version=1.0</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>量子计算控制装置、量子计算机及量子计算控制方法</t>
+          <t>蛋白质DDG预测模型优化方法、蛋白质DDG预测方法及相关装置</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>独立行政法人科学技术振兴机构</t>
+          <t>上海图灵智算量子科技有限公司 | 图灵智算量子科技(无锡)有限公司</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>中村泰信 | 田渊丰 | 玉手修平</t>
+          <t>丁灏 | 陆遥遥 | 唐可馨</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -661,34 +661,34 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>量子计算控制装置具备控制信号生成部和量子比特模块。量子比特模块具备观测部、量子比特基板部、控制电路部、观测电路部以及信号处理电路部。多个量子比特分组为由各量子比特彼此的位置关系相同的多个量子比特构成的多个组而配置在量子比特基板部上。控制信号生成部生成控制信号和命令信号，控制信号用于执行一个以上的种类的空间上均匀的第一操作及以比一个以上的种类的第一操作低的频度来进行的空间上不均匀的第二操作，命令信号用于使控制电路部执行第一操作及第二操作的控制，该第一操作及第二操作是针对量子比特基板部上的量子比特的操作。控制电路部将控制信号分支到组，根据命令信号，对控制信号向量子比特基板部上的各量子比特的送出进行控制。观测电路部观测接受了第一操作或第二操作的各量子比特的状态。信号处理电路部向观测部发送各量子比特的观测信号。</t>
+          <t>本发明的实施例提供了一种蛋白质DDG预测模型优化方法、蛋白质DDG预测方法及相关装置，涉及生物信息数据处理技术领域。该方法包括：获取野生型蛋白质三维结构数据、突变体蛋白质三维结构数据以及第一DDG值。分别将野生型蛋白质三维结构数据与突变体蛋白质三维结构数据输入蛋白质DDG初始预测模型中优化后的编码器，得到野生型蛋白质三维结构数据对应的第一特征向量以及突变体蛋白质三维结构数据对应的第二特征向量。基于变分量子线路，根据第一特征向量以及第二特征向量得到第二DDG值。根据第一DDG值与第二DDG值对蛋白质DDG初始预测模型进行迭代优化，得到蛋白质DDG预测模型。本发明可以有效提高蛋白质DDG的预测准确率。</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://analytics.zhihuiya.com/patent-view/abst?patentId=efec951d-1740-473f-842d-97180ce3a76d&amp;shareId=1FE8B6DF-4B44-81FE-235C-3B3890D5E284&amp;from=EXPORT&amp;signature=cWStYX30VcRxj2P%2BjMY8Zcter538VTu%2BbtjG7vto470%3D&amp;expire=94608000&amp;date=20260529T004546Z&amp;version=1.0</t>
+          <t>https://analytics.zhihuiya.com/patent-view/abst?patentId=672fd6cf-6f0e-41fc-8e84-33a2e4bdaf83&amp;shareId=1B475C3G-7GDG-8976-149D-791913G50906&amp;from=EXPORT&amp;signature=d02VwQytTfhj8BUFbVzJ6%2BlEuDDqhl88coYfbn6GIkc%3D&amp;expire=94608000&amp;date=20260605T004519Z&amp;version=1.0</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>原子的电子态分离器、原子干涉仪、原子跃迁频率测量装置、原子振荡器、光晶格钟、量子计算机及原子的电子态叠加态的生成方法</t>
+          <t>一种混合量子集成学习与MedMamba协同的医学图像分类方法</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>国立大学法人东京大学</t>
+          <t>重庆师范大学</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>香取秀俊</t>
+          <t>董玉民 | 吴高杰</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -698,34 +698,34 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>本发明的原子的电子态分离器(1)包括：原子供给部(11)、原子移动路径(12)、探测激光光源(13)和磁场生成部(M)。原子供给部(11)供给以一定速度在原子移动路径(12)中移动的原子。探测激光光源(13)向原子移动路径(12)内供给与原子移动路径(12)同轴地在与原子的运动方向相反或相同的方向上传播的探测激光。磁场生成部(M)通过在原子移动路径(12)中生成与原子移动路径(12)正交的磁场并进行与容许电偶极子跃迁的电子态的波函数混合，能够进行基于在时间和空间上同样的探测激光的时钟跃迁的脉冲激发。或者，磁屏蔽件通过屏蔽在原子移动路径(12)中施加的磁场并在空间上改变塞曼频移，从而能够通过在时间和空间上同样的探测激光对时钟跃迁进行脉冲激发。其结果，能够连续地进行原子跃迁的分光和探测激光的频率控制，提高原子钟的稳定度。</t>
+          <t>本发明涉及医学图像分类技术领域，具体涉及一种混合量子集成学习与MedMamba协同的医学图像分类方法，包括将医学原始图像输入到预设的U‑Net特征提取器中，从医学原始图像中提取与特定疾病相关的可解释特征，输出对应的特征向量；将输出的特征向量输入到预先训练完成的混合量子集成学习模型中，输出对应的第一预测分类概率；将医学原始图像输入到预设的MedMamba模型，输出对应的第二预测分类概率；根据输出的第一预测分类概率和第二预测分类概率，基于预设的医学图像分类概率融合计算公式，计算出该医学原始图像所对应的最终分类概率。</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://analytics.zhihuiya.com/patent-view/abst?patentId=826fc8c9-43e7-46de-ba8a-7944a1978dc4&amp;shareId=1FE8B6DF-4B44-81FE-235C-3B3890D5E284&amp;from=EXPORT&amp;signature=LlykcgPkjh3vLSNIh6JaxjqICxUxQMbBk6mblb38Uwg%3D&amp;expire=94608000&amp;date=20260529T004546Z&amp;version=1.0</t>
+          <t>https://analytics.zhihuiya.com/patent-view/abst?patentId=d4645b8f-948b-4f7c-94eb-d26e01cf645c&amp;shareId=1B475C3G-7GDG-8976-149D-791913G50906&amp;from=EXPORT&amp;signature=2IQKwh78EKfMwPKLHW8QbOFFwRyLz%2BgowZdt0cqiglI%3D&amp;expire=94608000&amp;date=20260605T004519Z&amp;version=1.0</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>基于FPGA的蒙特卡罗路径积分-模拟量子退火方法及系统</t>
+          <t>面向mRNA编码蛋白结构预测的智能算力调度系统和方法</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>西安电子科技大学</t>
+          <t>微观纪元(合肥)量子科技有限公司</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>朱畅华 | 李帅威 | 何先灯 | 魏建涛 | 权东晓 | 易运晖 | 赵楠 | 陈南</t>
+          <t>郑跃强 | 夏坚 | 管佳明 | 董景祥</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -735,17 +735,17 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>本发明公开了一种基于FPGA实现的蒙特卡罗路径积分‑模拟量子退火方法，主要解决现有蒙特卡罗路径积分‑模拟量子退火算法在CPU上运行时间效率低的问题，其实现方案包括:在Bram空间初始化原始矩阵；FPGA产生随机数以对原始矩阵进行随机操作得到新矩阵；并行计算新矩阵和原始矩阵势能项差值、动能项差值和哈密顿量差值；判断是否更新原始矩阵；选择执行更新操作后原始矩阵中势能项最小的矩阵作为当前的最优方案解；更新耦合系数不断进行迭代直到设定的迭代次数，得到最优解即为最终的最优路径。本发明大幅提升了运行的时间效率，相对于传统的蒙特卡罗路径积分‑模拟量子退火算法运行时间提高了79倍，可用于实时性要求高场景的无人机路由规划。</t>
+          <t>本发明公开了一种面向mRNA编码蛋白结构预测的智能算力调度系统、方法和电子设备，面向mRNA编码蛋白结构预测的智能算力调度系统包括：输入与任务管理层，用于获取并翻译mRNA序列，得到原子性子任务；智能感知与调度核心层，与输入与任务管理层连接，用于根据原子性子任务，生成对应的优化调度决策；异构算力资源层，与智能感知与调度核心层，用于根据优化调度决策，进行经典计算和/或量子计算，得到对应的经典计算结果和/或量子计算结果；输出与优化层，与异构算力资源层连接，用于根据经典计算结果和/或量子计算结果，生成蛋白质3D结构模型。本发明的系统能够提高蛋白结构预测结果的准确性、效率，还能够提高算力资源利用率。</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://analytics.zhihuiya.com/patent-view/abst?patentId=4995bc0f-40ae-45ff-a154-7460d307f8a1&amp;shareId=1FE8B6DF-4B44-81FE-235C-3B3890D5E284&amp;from=EXPORT&amp;signature=mw%2F8XzKpXOlI5GwRkITNxI8qXk7gfaPvM1rU8BWWW%2BY%3D&amp;expire=94608000&amp;date=20260529T004546Z&amp;version=1.0</t>
+          <t>https://analytics.zhihuiya.com/patent-view/abst?patentId=4d22a8d3-adf5-47dc-9aed-5c7d59d46b35&amp;shareId=1B475C3G-7GDG-8976-149D-791913G50906&amp;from=EXPORT&amp;signature=axXXCq5IhvK07YTz55KsVaL1hHumCPG6xLS3XnMhQoc%3D&amp;expire=94608000&amp;date=20260605T004519Z&amp;version=1.0</t>
         </is>
       </c>
     </row>

--- a/weekly_temp/patents_量子软件与算法.xlsx
+++ b/weekly_temp/patents_量子软件与算法.xlsx
@@ -493,59 +493,59 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>通过量子计算和量子通信的分布式机器学习</t>
+          <t>一种混合量子集成学习与MedMamba协同的医学图像分类方法</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>谷歌有限责任公司</t>
+          <t>重庆师范大学</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>GILBOA, DAR | MCCLEAN, JARROD RYAN</t>
+          <t>董玉民 | 吴高杰</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>公开专利</t>
+          <t>授权专利</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>一个实施例包括一种方法,该方法包括在具有多个量子节点和量子通信网络的分布式量子计算系统 (DQCS) 上接收第一输入。基于第一输入和一个模型,在多个节点中的第一个量子节点上执行第一量子计算。第一量子计算的输出通过量子通信网络传输到多个量子节点中的第二个量子节点。基于第一量子计算的输出和在第二量子节点上实施的量子断层扫描算法,计算出分布式计算的结果。</t>
+          <t>本发明涉及医学图像分类技术领域，具体涉及一种混合量子集成学习与MedMamba协同的医学图像分类方法，包括将医学原始图像输入到预设的U‑Net特征提取器中，从医学原始图像中提取与特定疾病相关的可解释特征，输出对应的特征向量；将输出的特征向量输入到预先训练完成的混合量子集成学习模型中，输出对应的第一预测分类概率；将医学原始图像输入到预设的MedMamba模型，输出对应的第二预测分类概率；根据输出的第一预测分类概率和第二预测分类概率，基于预设的医学图像分类概率融合计算公式，计算出该医学原始图像所对应的最终分类概率。</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://analytics.zhihuiya.com/patent-view/abst?patentId=41983739-7b03-4a29-8a94-d42bd288f1c3&amp;shareId=1B475C3G-7GDG-8976-149D-791913G50906&amp;from=EXPORT&amp;signature=x2zwu5O68qAiOi1FfzjLIcHII840OPb%2BA%2BBRigla0v4%3D&amp;expire=94608000&amp;date=20260605T004519Z&amp;version=1.0</t>
+          <t>https://analytics.zhihuiya.com/patent-view/abst?patentId=d4645b8f-948b-4f7c-94eb-d26e01cf645c&amp;shareId=1B475C3G-7GDG-8976-149D-791913G50906&amp;from=EXPORT&amp;signature=2IQKwh78EKfMwPKLHW8QbOFFwRyLz%2BgowZdt0cqiglI%3D&amp;expire=94608000&amp;date=20260605T004519Z&amp;version=1.0</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>光纤型激光功率量子控制装置、方法、激光发射设备</t>
+          <t>一种利用噪声诱导谱滤波效应的量子算法及系统</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>北京无线电计量测试研究所</t>
+          <t>中国科学院物理研究所</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>纪仟仟 | 薛潇博 | 韩蕾 | 申彤 | 苏亚北 | 张升康 | 葛军</t>
+          <t>张士欣</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>授权专利</t>
+          <t>公开专利</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -555,29 +555,29 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>本说明书公开了一种光纤型激光功率量子控制装置、方法、激光发射设备，以提高激光功率的抗干扰能力和稳定度。本发明装置包括：第一支路，配置为对激光器输出的激光，经过声光调制器输出0级衍射光，经光纤隔离器后输出待稳功率激光；第二支路为反馈调节支路，将第一支路中的待稳功率激光作为监测信号，导入原子钟使原子钟的输出频率随之改变，基于该输出频率与给定输出频率之间的偏差，通过反馈控制方法对第一支路中激光偏振态进行调整，以稳定输出激光的功率。本发明中，使用全光纤结构的量子控制装置具有结构简单、体积小巧、成本低、重量轻、实验装置难度低、免于调试空间光路、不易受外界杂散光影响的优势，并且提高了激光功率稳定度。</t>
+          <t>本发明提供一种利用噪声诱导谱滤波效应的量子算法，用于优化目标量子线路以获得目标量子线路的全局最优解，包括：S1、为待优化的目标量子线路构建添加量子噪声的含噪代理模型，以用于代理每一个量子逻辑门操作后量子态受噪声影响的演化过程；S2、在包含量子噪声的代理模型上进行第一次梯度下降优化处理，以获得目标量子线路的预训练线路参数；S3、将预训练线路参数加载至模拟目标量子线路的无噪或低噪环境中以完成参数迁移；S4、在完成参数迁移的模拟目标量子线路的环境中，基于目标量子线路的损失函数对第二次线路参数做梯度下降直至收敛以获得目标量子线路的全局最优解。</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://analytics.zhihuiya.com/patent-view/abst?patentId=819b526b-053e-44fe-abb9-bc58efecb2c1&amp;shareId=1B475C3G-7GDG-8976-149D-791913G50906&amp;from=EXPORT&amp;signature=eDjSYHnwujwUnfnLRX7a6lcTR7W36aTMxSFLUA%2BMZtU%3D&amp;expire=94608000&amp;date=20260605T004519Z&amp;version=1.0</t>
+          <t>https://analytics.zhihuiya.com/patent-view/abst?patentId=24cbbb68-c81d-4b5b-b94a-2be4e49de07d&amp;shareId=1B475C3G-7GDG-8976-149D-791913G50906&amp;from=EXPORT&amp;signature=VCjvMWx4jFgCYc3vRdRVn7FSnZLpmMAw1FN4plCYmA4%3D&amp;expire=94608000&amp;date=20260605T004519Z&amp;version=1.0</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>偏振控制的激光功率量子稳定装置、方法、激光发射设备</t>
+          <t>量子系统中用于学习双能级系统缺陷的系统和方法</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>北京无线电计量测试研究所</t>
+          <t>谷歌有限责任公司</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>纪仟仟 | 薛潇博 | 韩蕾 | 申彤 | 苏亚北 | 张升康 | 葛军</t>
+          <t>NIU, YUEZHEN | SMELYANSKIY, VADIM | BOIXO CASTRILLO, SERGIO | KLIMOV, PAUL VICTOR</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -592,29 +592,29 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>本说明书公开了一种偏振控制的激光功率量子稳定装置、方法、激光发射设备，以提高激光功率的稳定性。本发明装置包括：激光功率调整单元，配置为对激光器输出的线偏振光，采用偏振控制器进行激光偏振态的调整，并经保偏传输后输出待稳功率激光；反馈控制单元，配置为以待稳功率激光作为监测对象，将其导入原子钟，使原子钟输出频率随之改变，基于该输出频率与给定输出频率之间的偏差，通过反馈控制方法对激光功率调整单元中激光偏振态进行调整，以稳定输出激光的功率。本发明抗环境干扰能力强、减小了传统方法里激光偏振变化对功率稳定的影响，提高了系统稳定功率微小变化的灵敏度和响应能力，更加精准的进行稳定激光功率的控制。</t>
+          <t>本公开的示例性方面提供了用于学习量子计算系统模型的机器学习模型参数的系统和方法。具体而言,本公开的示例性方面涉及用于学习深度神经网络的系统和方法,该深度神经网络配置为预测物理模型的参数值,该物理模型模拟量子门运行期间一个或多个量子比特与一个或多个双能级系统(TLS)缺陷之间相互作用的量子动力学,并通过进化算法实现。</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://analytics.zhihuiya.com/patent-view/abst?patentId=676a11df-8175-4c2e-a0bf-56f414fb96a8&amp;shareId=1B475C3G-7GDG-8976-149D-791913G50906&amp;from=EXPORT&amp;signature=VSiYnCmNha%2BQaeQPLSGbuT%2FMEBPmMphs47whZ4h3atw%3D&amp;expire=94608000&amp;date=20260605T004519Z&amp;version=1.0</t>
+          <t>https://analytics.zhihuiya.com/patent-view/abst?patentId=c6ef9718-67a1-4f38-aa10-389e62c2a090&amp;shareId=1B475C3G-7GDG-8976-149D-791913G50906&amp;from=EXPORT&amp;signature=tpFIzDWosEvWVa%2FVDhcYRV7kjTfqt3DHk5CkfOjOxvw%3D&amp;expire=94608000&amp;date=20260605T004519Z&amp;version=1.0</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>太赫兹光谱量子弱测量方法、系统及应用</t>
+          <t>多特征值的量子相位估计</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>中国科学院深圳先进技术研究院</t>
+          <t>谷歌有限责任公司</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>常天英 | 崔洪亮 | 路星星 | 魏东山 | 汪岳峰</t>
+          <t>BABBUSH, RYAN | DING, NAN</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -629,29 +629,29 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>本发明提供了太赫兹光谱量子弱测量方法、系统及应用，属于太赫兹技术领域，该太赫兹光谱量子弱测量方法应用于太赫兹光谱量子弱测量系统，所述系统包括第一偏振片、第二偏振片、太赫兹时域光谱单元、发射端、探测端及样品载体，本发明提出的基于量子弱值放大效应的太赫兹量子弱测量方法及系统，能够突破目前太赫兹技术的痕量检测极限。本发明通过选定一个太赫兹偏振状态(前选态)，被测量的微小变化对其产生一种“微”扰动，再用强测量将被扰动系统态投影到后选态上，进而建立太赫兹量子弱测量体系；大多手性药物在太赫兹波段具有共振吸收性，有益于利用手性分子的旋光度微变化作为弱耦合作用，实现手性药物的高灵敏构象识别。</t>
+          <t>用于量子相位估计的方法、系统和装置。在一个方面,一种装置包括:量子电路,该量子电路包括:第一量子寄存器,该第一量子寄存器包含至少一个辅助量子比特;量子门,该量子门至少包含:(i) 两个哈达玛门,(ii) 一个相位门,(iii) 一个酉算符,以及 (iv) 一个测量算符;第二量子寄存器,该第二量子寄存器包含一个或多个量子比特,其中,该第二量子寄存器被制备在任意量子态,该任意量子态并非酉算符的本征态;以及相位学习系统,该系统配置为对所述量子电路执行相位估计实验,其包括:在每次相位估计实验中重复测量辅助量子比特的状态,以确定辅助量子比特状态的期望值并学习酉算符本征值的相位。</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://analytics.zhihuiya.com/patent-view/abst?patentId=c9746448-bedc-4316-b621-fe01a87980db&amp;shareId=1B475C3G-7GDG-8976-149D-791913G50906&amp;from=EXPORT&amp;signature=wi1MMHbFVv7qi%2BmluFU5HXTRO59DnQ5Cn1nbNzzY1ak%3D&amp;expire=94608000&amp;date=20260605T004519Z&amp;version=1.0</t>
+          <t>https://analytics.zhihuiya.com/patent-view/abst?patentId=3ff4d9b9-bee4-4f43-a63e-83697c266b42&amp;shareId=1B475C3G-7GDG-8976-149D-791913G50906&amp;from=EXPORT&amp;signature=mp3sCPeem1ukTRJoe96BsI2l6e%2FQinIqLtMHn%2BRHjDw%3D&amp;expire=94608000&amp;date=20260605T004519Z&amp;version=1.0</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>蛋白质DDG预测模型优化方法、蛋白质DDG预测方法及相关装置</t>
+          <t>处理表面代码匹配图中高亮顶点的垂直对</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>上海图灵智算量子科技有限公司 | 图灵智算量子科技(无锡)有限公司</t>
+          <t>亚马逊科技公司</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>丁灏 | 陆遥遥 | 唐可馨</t>
+          <t>CHAMBERLAND, CHRISTOPHER | GONCALVES, LUIS | SIVARAJAH, PRASAHNT | PETERSON, ERIC CHRISTOPHER | GRIMBERG, SEBASTIAN JOHANNES</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -666,29 +666,29 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>本发明的实施例提供了一种蛋白质DDG预测模型优化方法、蛋白质DDG预测方法及相关装置，涉及生物信息数据处理技术领域。该方法包括：获取野生型蛋白质三维结构数据、突变体蛋白质三维结构数据以及第一DDG值。分别将野生型蛋白质三维结构数据与突变体蛋白质三维结构数据输入蛋白质DDG初始预测模型中优化后的编码器，得到野生型蛋白质三维结构数据对应的第一特征向量以及突变体蛋白质三维结构数据对应的第二特征向量。基于变分量子线路，根据第一特征向量以及第二特征向量得到第二DDG值。根据第一DDG值与第二DDG值对蛋白质DDG初始预测模型进行迭代优化，得到蛋白质DDG预测模型。本发明可以有效提高蛋白质DDG的预测准确率。</t>
+          <t>本发明公开了用于降低量子表面码电路级噪声量子纠错过程中,经过第一解码阶段(例如,通过本地解码器)后,多轮伴随式测量结果的伴随式密度的技术。这些降低伴随式密度的技术可以包括伴随式坍缩和/或垂直清理技术。在伴随式坍缩技术中,可以将测量结果体分割成多个片层,然后对各个片层进行坍缩,从而移除垂直方向上的突出显示顶点对。在垂直清理技术中,可以在第一解码阶段之后,直接从匹配图中移除垂直方向上的突出显示顶点对。移除垂直方向上的突出显示顶点对之后,测量结果将在第二全局解码阶段进行解码。这种技术能够实现快速解码,并降低使用量子表面码实现的量子算法的纠错轮次延迟时间。</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://analytics.zhihuiya.com/patent-view/abst?patentId=672fd6cf-6f0e-41fc-8e84-33a2e4bdaf83&amp;shareId=1B475C3G-7GDG-8976-149D-791913G50906&amp;from=EXPORT&amp;signature=d02VwQytTfhj8BUFbVzJ6%2BlEuDDqhl88coYfbn6GIkc%3D&amp;expire=94608000&amp;date=20260605T004519Z&amp;version=1.0</t>
+          <t>https://analytics.zhihuiya.com/patent-view/abst?patentId=96463724-9d1a-4d5a-aa6c-f0cb66a03c97&amp;shareId=1B475C3G-7GDG-8976-149D-791913G50906&amp;from=EXPORT&amp;signature=GiTw1TTaYYBdtJUzMrqsSFBxcCJdNcz%2B7jZXuZxHhqo%3D&amp;expire=94608000&amp;date=20260605T004519Z&amp;version=1.0</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>一种混合量子集成学习与MedMamba协同的医学图像分类方法</t>
+          <t>一种用于求解离散二次模型的混合算法的系统和方法</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>重庆师范大学</t>
+          <t>D WAVE 系统公司</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>董玉民 | 吴高杰</t>
+          <t>エスファハニ,ホセイン,サデギ | ベルヌーディ,ウィリアム,ダヴリュー. | ラーマニ,モーセン</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -698,34 +698,35 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>本发明涉及医学图像分类技术领域，具体涉及一种混合量子集成学习与MedMamba协同的医学图像分类方法，包括将医学原始图像输入到预设的U‑Net特征提取器中，从医学原始图像中提取与特定疾病相关的可解释特征，输出对应的特征向量；将输出的特征向量输入到预先训练完成的混合量子集成学习模型中，输出对应的第一预测分类概率；将医学原始图像输入到预设的MedMamba模型，输出对应的第二预测分类概率；根据输出的第一预测分类概率和第二预测分类概率，基于预设的医学图像分类概率融合计算公式，计算出该医学原始图像所对应的最终分类概率。</t>
+          <t>采用吉布斯采样和交叉玻尔兹曼更新法求解离散二次模型。 
+该方法基于每个变量与其他变量的相互作用,计算每个变量各状态的能量,计算指数权重,并计算与该指数权重成正比的归一化概率。每个变量的能量是根据其自身大小和所有其他变量的当前状态计算的,计算指数权重,计算每个变量的可行域,并计算与该指数权重和所满足的约束条件成正比的归一化概率。该方法通过混合计算系统执行,为每个变量获得两个候选值,构建一个使用二进制值来确定每个变量应取哪个候选值的哈密顿量,然后基于该哈密顿量构建一个二维二次模型。通过量子处理器从该二维二次模型中获取样本。</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://analytics.zhihuiya.com/patent-view/abst?patentId=d4645b8f-948b-4f7c-94eb-d26e01cf645c&amp;shareId=1B475C3G-7GDG-8976-149D-791913G50906&amp;from=EXPORT&amp;signature=2IQKwh78EKfMwPKLHW8QbOFFwRyLz%2BgowZdt0cqiglI%3D&amp;expire=94608000&amp;date=20260605T004519Z&amp;version=1.0</t>
+          <t>https://analytics.zhihuiya.com/patent-view/abst?patentId=b5843080-6f14-46bd-a875-ecfa9ca57327&amp;shareId=1B475C3G-7GDG-8976-149D-791913G50906&amp;from=EXPORT&amp;signature=vV8i09e1sZvHnlordWP6TkjMzkk%2FxFyzW0zW%2FSPCnWM%3D&amp;expire=94608000&amp;date=20260605T004519Z&amp;version=1.0</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>面向mRNA编码蛋白结构预测的智能算力调度系统和方法</t>
+          <t>磁化自旋量子人工神经网络装置</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>微观纪元(合肥)量子科技有限公司</t>
+          <t>EFRAM</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>郑跃强 | 夏坚 | 管佳明 | 董景祥</t>
+          <t>강희복</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -735,17 +736,23 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>本发明公开了一种面向mRNA编码蛋白结构预测的智能算力调度系统、方法和电子设备，面向mRNA编码蛋白结构预测的智能算力调度系统包括：输入与任务管理层，用于获取并翻译mRNA序列，得到原子性子任务；智能感知与调度核心层，与输入与任务管理层连接，用于根据原子性子任务，生成对应的优化调度决策；异构算力资源层，与智能感知与调度核心层，用于根据优化调度决策，进行经典计算和/或量子计算，得到对应的经典计算结果和/或量子计算结果；输出与优化层，与异构算力资源层连接，用于根据经典计算结果和/或量子计算结果，生成蛋白质3D结构模型。本发明的系统能够提高蛋白结构预测结果的准确性、效率，还能够提高算力资源利用率。</t>
+          <t>一个线性组合(48)节点、一个激活函数(49)、一个输出数据(Y1)、m 个输入数据 Xi 终端和 m 个权重区域(400)元素构成一个独立的层。 
+换句话说,该装置是通过形成与输出数据数量 (Yi) 相等的独立层来构建的。 
+例如,如果由 n 个输出数据 (Yn) 组成,则该设备由形成 n 个独立层构成。 
+当由 m 个输入数据 Xi 端子和 n 个输出数据 (Yn) 端子组成时,该设备通过形成 n 个独立层进行配置。 
+ m 个输入数据端子 Xi 通过 TLV(层直通)连接到 n 个独立的层。 
+例如,第一个输入端子 X1 通过 TLV(层通孔)连接到 n 个独立的层。 
+此外,第 m 个输入值 Xm 端子的特点是,它通过 TLV(层间过孔)与 n 个独立的层中的每一个都相连。</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://analytics.zhihuiya.com/patent-view/abst?patentId=4d22a8d3-adf5-47dc-9aed-5c7d59d46b35&amp;shareId=1B475C3G-7GDG-8976-149D-791913G50906&amp;from=EXPORT&amp;signature=axXXCq5IhvK07YTz55KsVaL1hHumCPG6xLS3XnMhQoc%3D&amp;expire=94608000&amp;date=20260605T004519Z&amp;version=1.0</t>
+          <t>https://analytics.zhihuiya.com/patent-view/abst?patentId=0b17bd05-b7e9-471d-830e-01cd79f8a5c6&amp;shareId=1B475C3G-7GDG-8976-149D-791913G50906&amp;from=EXPORT&amp;signature=4ZmPz4kCFhX3NXF%2Fsvdo8zYjUmJ7GW%2BWZQsGLW7qNos%3D&amp;expire=94608000&amp;date=20260605T004519Z&amp;version=1.0</t>
         </is>
       </c>
     </row>

--- a/weekly_temp/patents_量子软件与算法.xlsx
+++ b/weekly_temp/patents_量子软件与算法.xlsx
@@ -456,17 +456,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>基于量子干涉采样的组合优化</t>
+          <t>系统</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>谷歌有限责任公司</t>
+          <t>软银集团股份有限公司</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>JORDAN, STEPHEN, PAUL</t>
+          <t>北山 翔平</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -476,71 +476,87 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>本发明公开了一种用于优化包含一组自由度 (DOF) 和一组针对该 DOF 的约束的系统的方法。每个约束与该 DOF 集的一个子集相关联。该方法包括确定第一个多项式函数。量子计算系统 (QCS) 的一组量子比特在第一量子态下准备。在第一量子态下准备该组量子比特后,QCS 对该组量子比特执行一组幺正运算。在该组量子比特执行该组幺正运算后,QCS 通过对该组量子比特中的每个量子比特执行第一次测量操作来生成第一组可观测量。基于第一组可观测量确定一组值。</t>
+          <t>我们提供系统。 
+ [解决方案] 
+一种利用放置在家庭环境中的录音设备来收集儿童行为信息的方法, 
+一种利用智能模型分析已收集到的各种信息来评估儿童发展特征的方法; 
+根据评估结果,提出一种促进儿童教育和发展的建议方法, 
+一种分析儿童情绪状态并根据需要提供即时报告的方法, 
+一种通过持续的数据积累来预测发育模式并及早发现潜在发育挑战的方法, 
+一种利用移动自主设备监测儿童活动并提供互动式教育体验的方法, 
+该系统包括根据分析结果向家长提供即时反馈并推荐个性化育儿方法的手段。</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://analytics.zhihuiya.com/patent-view/abst?patentId=beb237b0-424b-4221-a72c-bd637552d779&amp;shareId=1B475C3G-7GDG-8976-149D-791913G50906&amp;from=EXPORT&amp;signature=Fc9PUiPsEY%2BdIF3wHPUrxnJZNZBVa%2BvhLOLvvonDkE8%3D&amp;expire=94608000&amp;date=20260605T004519Z&amp;version=1.0</t>
+          <t>https://analytics.zhihuiya.com/patent-view/abst?patentId=f36cf315-d771-4bd4-bd79-851b2461e788&amp;shareId=198G292E-EE74-750G-3C47-5E63C2EB5B01&amp;from=EXPORT&amp;signature=aPG1NpV1V4CDLw5vBIOMLwos9FU5AfJFQu6bhMP%2BD9c%3D&amp;expire=94608000&amp;date=20260626T004645Z&amp;version=1.0</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>一种混合量子集成学习与MedMamba协同的医学图像分类方法</t>
+          <t>系统</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>重庆师范大学</t>
+          <t>软银集团股份有限公司</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>董玉民 | 吴高杰</t>
+          <t>鈴木 貴雄</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>授权专利</t>
+          <t>公开专利</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>本发明涉及医学图像分类技术领域，具体涉及一种混合量子集成学习与MedMamba协同的医学图像分类方法，包括将医学原始图像输入到预设的U‑Net特征提取器中，从医学原始图像中提取与特定疾病相关的可解释特征，输出对应的特征向量；将输出的特征向量输入到预先训练完成的混合量子集成学习模型中，输出对应的第一预测分类概率；将医学原始图像输入到预设的MedMamba模型，输出对应的第二预测分类概率；根据输出的第一预测分类概率和第二预测分类概率，基于预设的医学图像分类概率融合计算公式，计算出该医学原始图像所对应的最终分类概率。</t>
+          <t>我们提供系统。 
+ [解决方案] 
+收集和分析多语言信息的方法, 
+一种利用生成算法设计新的标准表示的方法, 
+将多语言信息转换为标准化表达并进行压缩的方法
+一种利用转换后的信息优化预测模型的方法, 
+一种利用预测模型与用户进行双向通信的方法, 
+一种实时呈现翻译信息的方式, 
+包含此功能的系统。</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://analytics.zhihuiya.com/patent-view/abst?patentId=d4645b8f-948b-4f7c-94eb-d26e01cf645c&amp;shareId=1B475C3G-7GDG-8976-149D-791913G50906&amp;from=EXPORT&amp;signature=2IQKwh78EKfMwPKLHW8QbOFFwRyLz%2BgowZdt0cqiglI%3D&amp;expire=94608000&amp;date=20260605T004519Z&amp;version=1.0</t>
+          <t>https://analytics.zhihuiya.com/patent-view/abst?patentId=05206804-f180-4003-a513-4128990ff3d7&amp;shareId=198G292E-EE74-750G-3C47-5E63C2EB5B01&amp;from=EXPORT&amp;signature=mX%2F6Si8MtE3gzweHffnMsOY2wPMMXXMimxAnhfRn2dk%3D&amp;expire=94608000&amp;date=20260626T004645Z&amp;version=1.0</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>一种利用噪声诱导谱滤波效应的量子算法及系统</t>
+          <t>制造量子器件的方法</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>中国科学院物理研究所</t>
+          <t>富士通株式会社</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>张士欣</t>
+          <t>MIYATAKE, TETSUYA</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -550,209 +566,216 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>本发明提供一种利用噪声诱导谱滤波效应的量子算法，用于优化目标量子线路以获得目标量子线路的全局最优解，包括：S1、为待优化的目标量子线路构建添加量子噪声的含噪代理模型，以用于代理每一个量子逻辑门操作后量子态受噪声影响的演化过程；S2、在包含量子噪声的代理模型上进行第一次梯度下降优化处理，以获得目标量子线路的预训练线路参数；S3、将预训练线路参数加载至模拟目标量子线路的无噪或低噪环境中以完成参数迁移；S4、在完成参数迁移的模拟目标量子线路的环境中，基于目标量子线路的损失函数对第二次线路参数做梯度下降直至收敛以获得目标量子线路的全局最优解。</t>
+          <t>一种制造量子器件(100、200)的方法,包括:将包括色心(21)的金刚石衬底(30)键合到设置在支撑衬底(10)上的层(32);在键合金刚石衬底之后,通过蚀刻金刚石衬底形成包括色心的第一部分(40)和具有相对于第一部分的侧壁(41)倾斜的倾斜表面(43)的第二部分(42);在倾斜表面上形成金属膜(45);以及通过将由金属膜反射的激光束发射到第一部分的侧壁上,在比色心更远离层的第一位置处切割第一部分,形成第一光波导部分(20)。</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://analytics.zhihuiya.com/patent-view/abst?patentId=24cbbb68-c81d-4b5b-b94a-2be4e49de07d&amp;shareId=1B475C3G-7GDG-8976-149D-791913G50906&amp;from=EXPORT&amp;signature=VCjvMWx4jFgCYc3vRdRVn7FSnZLpmMAw1FN4plCYmA4%3D&amp;expire=94608000&amp;date=20260605T004519Z&amp;version=1.0</t>
+          <t>https://analytics.zhihuiya.com/patent-view/abst?patentId=147d295d-d8ec-42f5-992e-6849a8347ea5&amp;shareId=198G292E-EE74-750G-3C47-5E63C2EB5B01&amp;from=EXPORT&amp;signature=1LRVFVPrGAVE63BzDm9n2Gd4dL4mu06NQBSQPD7%2FE3s%3D&amp;expire=94608000&amp;date=20260626T004645Z&amp;version=1.0</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>量子系统中用于学习双能级系统缺陷的系统和方法</t>
+          <t>将应用迁移到后量子密码术(PQC)状态的工作量的估计</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>谷歌有限责任公司</t>
+          <t>塔塔顾问服务有限公司</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>NIU, YUEZHEN | SMELYANSKIY, VADIM | BOIXO CASTRILLO, SERGIO | KLIMOV, PAUL VICTOR</t>
+          <t>BHOWMICK, AMIT | VIDHANI, KUMAR MANSUKHLAL | ALASINGARA, BHATTACHAR</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>授权专利</t>
+          <t>公开专利</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>本公开的示例性方面提供了用于学习量子计算系统模型的机器学习模型参数的系统和方法。具体而言,本公开的示例性方面涉及用于学习深度神经网络的系统和方法,该深度神经网络配置为预测物理模型的参数值,该物理模型模拟量子门运行期间一个或多个量子比特与一个或多个双能级系统(TLS)缺陷之间相互作用的量子动力学,并通过进化算法实现。</t>
+          <t>过去几十年来,准确估计完成应用迁移所需的代码行(LoC)的能力一直是一个挑战。本文公开的实施例提供了一种用于估计将应用迁移到后量子密码(PQC)状态的工作量的方法和系统。基于针对存在于精细分片输出和精细耦合输出中的一个或多个组件所确定的循环复杂度来估计该系统。此外,使用循环复杂度和受一个或多个密码API影响的LoC的数量来估计迁移的工作量。</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://analytics.zhihuiya.com/patent-view/abst?patentId=c6ef9718-67a1-4f38-aa10-389e62c2a090&amp;shareId=1B475C3G-7GDG-8976-149D-791913G50906&amp;from=EXPORT&amp;signature=tpFIzDWosEvWVa%2FVDhcYRV7kjTfqt3DHk5CkfOjOxvw%3D&amp;expire=94608000&amp;date=20260605T004519Z&amp;version=1.0</t>
+          <t>https://analytics.zhihuiya.com/patent-view/abst?patentId=33c6710b-c21a-4984-bbe8-048106c16b2b&amp;shareId=198G292E-EE74-750G-3C47-5E63C2EB5B01&amp;from=EXPORT&amp;signature=Wap4suo%2BlI8eezOxtgJgww9rFAJGRuV8FW%2FcLrGzzts%3D&amp;expire=94608000&amp;date=20260626T004645Z&amp;version=1.0</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>多特征值的量子相位估计</t>
+          <t>减少量子计算机中使用的量子位</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>谷歌有限责任公司</t>
+          <t>微软技术许可有限责任公司</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>BABBUSH, RYAN | DING, NAN</t>
+          <t>SU, YUAN | KANG, CHRISTOPHER THOMAS</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>授权专利</t>
+          <t>公开专利</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>用于量子相位估计的方法、系统和装置。在一个方面,一种装置包括:量子电路,该量子电路包括:第一量子寄存器,该第一量子寄存器包含至少一个辅助量子比特;量子门,该量子门至少包含:(i) 两个哈达玛门,(ii) 一个相位门,(iii) 一个酉算符,以及 (iv) 一个测量算符;第二量子寄存器,该第二量子寄存器包含一个或多个量子比特,其中,该第二量子寄存器被制备在任意量子态,该任意量子态并非酉算符的本征态;以及相位学习系统,该系统配置为对所述量子电路执行相位估计实验,其包括:在每次相位估计实验中重复测量辅助量子比特的状态,以确定辅助量子比特状态的期望值并学习酉算符本征值的相位。</t>
+          <t>本公开的各方面包括用于操作量子电路的过程。各方面包括利用单元演化对第一被乘数和第二被乘数执行哈密尔顿块编码,分别产生第一中间算子和第二中间算子。各方面包括对第一中间算子执行第一门和对第二中间算子执行第二门,分别产生修改的第一中间算子和修改的第二中间算子。各方面包括执行交换子积公式以组合修改的第一中间算子和修改的第二中间算子,产生组合算子,并且对组合算子执行另一第一门和另一第二门,产生修改的组合算子。另一第二门包括另一第一门的共轭转置。在量子电路上利用两个辅助量子位。</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://analytics.zhihuiya.com/patent-view/abst?patentId=3ff4d9b9-bee4-4f43-a63e-83697c266b42&amp;shareId=1B475C3G-7GDG-8976-149D-791913G50906&amp;from=EXPORT&amp;signature=mp3sCPeem1ukTRJoe96BsI2l6e%2FQinIqLtMHn%2BRHjDw%3D&amp;expire=94608000&amp;date=20260605T004519Z&amp;version=1.0</t>
+          <t>https://analytics.zhihuiya.com/patent-view/abst?patentId=99cacae8-3277-48aa-bcd5-40b7bc9556c9&amp;shareId=198G292E-EE74-750G-3C47-5E63C2EB5B01&amp;from=EXPORT&amp;signature=HRm5nYt9eqUsmWz0RhgB6gBmUNjJzwQKKPPJWB%2BP1zQ%3D&amp;expire=94608000&amp;date=20260626T004645Z&amp;version=1.0</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>处理表面代码匹配图中高亮顶点的垂直对</t>
+          <t>量子点阵列的制造和有效接触各种栅极的方式</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>亚马逊科技公司</t>
+          <t>原子能和替代能源委员会</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>CHAMBERLAND, CHRISTOPHER | GONCALVES, LUIS | SIVARAJAH, PRASAHNT | PETERSON, ERIC CHRISTOPHER | GRIMBERG, SEBASTIAN JOHANNES</t>
+          <t>BERTRAND, BENOIT</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>授权专利</t>
+          <t>公开专利</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>本发明公开了用于降低量子表面码电路级噪声量子纠错过程中,经过第一解码阶段(例如,通过本地解码器)后,多轮伴随式测量结果的伴随式密度的技术。这些降低伴随式密度的技术可以包括伴随式坍缩和/或垂直清理技术。在伴随式坍缩技术中,可以将测量结果体分割成多个片层,然后对各个片层进行坍缩,从而移除垂直方向上的突出显示顶点对。在垂直清理技术中,可以在第一解码阶段之后,直接从匹配图中移除垂直方向上的突出显示顶点对。移除垂直方向上的突出显示顶点对之后,测量结果将在第二全局解码阶段进行解码。这种技术能够实现快速解码,并降低使用量子表面码实现的量子算法的纠错轮次延迟时间。</t>
+          <t>量子电子器件包括:- 用于容纳量子点的活性区域 (20),以及,- 紧贴该器件一个表面的:a) 多条网格线 (G11、G12、G13、G14),这些网格线彼此电隔离,并且每条网格线覆盖活性区域 (20) 的一部分;以及 b) 重建促进岛 (14-17、I4a-I7a),每条网格线上至少有一个岛,重建促进岛彼此间隔距离 (D1、D2、D3),每个重建促进岛包括一个侧翼,网格线的侧部 (P4-P7) 沿该侧翼延伸,该器件还包括至少一个电触点 (P4-P7),用于接触至少一条给定的网格线 (G11、G12、G13、G14)。至少一个电触点位于沿触点重建促进岛侧边延伸的给定网格线的侧面上(14-17,I4a-I7a)。</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://analytics.zhihuiya.com/patent-view/abst?patentId=96463724-9d1a-4d5a-aa6c-f0cb66a03c97&amp;shareId=1B475C3G-7GDG-8976-149D-791913G50906&amp;from=EXPORT&amp;signature=GiTw1TTaYYBdtJUzMrqsSFBxcCJdNcz%2B7jZXuZxHhqo%3D&amp;expire=94608000&amp;date=20260605T004519Z&amp;version=1.0</t>
+          <t>https://analytics.zhihuiya.com/patent-view/abst?patentId=92bb9f73-0f44-40dc-b3b6-f7273088bdf1&amp;shareId=198G292E-EE74-750G-3C47-5E63C2EB5B01&amp;from=EXPORT&amp;signature=uBapswM4SNm755iLb%2FLWAbPS5zRkhGk5%2FKk2ude%2F9L4%3D&amp;expire=94608000&amp;date=20260626T004645Z&amp;version=1.0</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>一种用于求解离散二次模型的混合算法的系统和方法</t>
+          <t>系统</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>D WAVE 系统公司</t>
+          <t>软银集团股份有限公司</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>エスファハニ,ホセイン,サデギ | ベルヌーディ,ウィリアム,ダヴリュー. | ラーマニ,モーセン</t>
+          <t>五條 眞樹</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>授权专利</t>
+          <t>公开专利</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>采用吉布斯采样和交叉玻尔兹曼更新法求解离散二次模型。 
-该方法基于每个变量与其他变量的相互作用,计算每个变量各状态的能量,计算指数权重,并计算与该指数权重成正比的归一化概率。每个变量的能量是根据其自身大小和所有其他变量的当前状态计算的,计算指数权重,计算每个变量的可行域,并计算与该指数权重和所满足的约束条件成正比的归一化概率。该方法通过混合计算系统执行,为每个变量获得两个候选值,构建一个使用二进制值来确定每个变量应取哪个候选值的哈密顿量,然后基于该哈密顿量构建一个二维二次模型。通过量子处理器从该二维二次模型中获取样本。</t>
+          <t>我们提供系统。 
+ [解决方案] 
+为了支持跨文化交流, 
+收集不同文化信息的方法
+一种利用自然语言处理技术分析用户输入以了解文化背景的方法
+一种根据分析结果制定合适的沟通策略的方法, 
+向用户展示生成策略的一种方式, 
+基于乘客文化背景的语音导览优化方法
+包含此功能的系统。</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://analytics.zhihuiya.com/patent-view/abst?patentId=b5843080-6f14-46bd-a875-ecfa9ca57327&amp;shareId=1B475C3G-7GDG-8976-149D-791913G50906&amp;from=EXPORT&amp;signature=vV8i09e1sZvHnlordWP6TkjMzkk%2FxFyzW0zW%2FSPCnWM%3D&amp;expire=94608000&amp;date=20260605T004519Z&amp;version=1.0</t>
+          <t>https://analytics.zhihuiya.com/patent-view/abst?patentId=6db73478-fd06-4259-907b-029fbe6fe32e&amp;shareId=198G292E-EE74-750G-3C47-5E63C2EB5B01&amp;from=EXPORT&amp;signature=goKIEMdPH0oyF7LWIV6ShkWi2LLkDhTR3t6KZbRyaAE%3D&amp;expire=94608000&amp;date=20260626T004645Z&amp;version=1.0</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>磁化自旋量子人工神经网络装置</t>
+          <t>系统</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>EFRAM</t>
+          <t>软银集团股份有限公司</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>강희복</t>
+          <t>松崎 達彦</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>授权专利</t>
+          <t>公开专利</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>一个线性组合(48)节点、一个激活函数(49)、一个输出数据(Y1)、m 个输入数据 Xi 终端和 m 个权重区域(400)元素构成一个独立的层。 
-换句话说,该装置是通过形成与输出数据数量 (Yi) 相等的独立层来构建的。 
-例如,如果由 n 个输出数据 (Yn) 组成,则该设备由形成 n 个独立层构成。 
-当由 m 个输入数据 Xi 端子和 n 个输出数据 (Yn) 端子组成时,该设备通过形成 n 个独立层进行配置。 
- m 个输入数据端子 Xi 通过 TLV(层直通)连接到 n 个独立的层。 
-例如,第一个输入端子 X1 通过 TLV(层通孔)连接到 n 个独立的层。 
-此外,第 m 个输入值 Xm 端子的特点是,它通过 TLV(层间过孔)与 n 个独立的层中的每一个都相连。</t>
+          <t>我们提供系统。 
+ [解决方案] 
+一种利用自然语言处理算法分析电子邮件正文,并从中提取预定信息元素的方法; 
+一种基于提取的信息元素自动生成电子邮件主题行的方法, 
+一种利用生成式人工智能模型生成与电子支付等事件相关的电子邮件主题行的方法, 
+一种在移动信息终端设备的用户界面上显示生成的电子邮件主题的方法, 
+包含此功能的系统。</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://analytics.zhihuiya.com/patent-view/abst?patentId=0b17bd05-b7e9-471d-830e-01cd79f8a5c6&amp;shareId=1B475C3G-7GDG-8976-149D-791913G50906&amp;from=EXPORT&amp;signature=4ZmPz4kCFhX3NXF%2Fsvdo8zYjUmJ7GW%2BWZQsGLW7qNos%3D&amp;expire=94608000&amp;date=20260605T004519Z&amp;version=1.0</t>
+          <t>https://analytics.zhihuiya.com/patent-view/abst?patentId=61040822-06cc-4bc7-ac72-f5d29ba20241&amp;shareId=198G292E-EE74-750G-3C47-5E63C2EB5B01&amp;from=EXPORT&amp;signature=GmrQFBGaBjPoMklYAlWW6mwoDp5U6B97cTe2leqt55A%3D&amp;expire=94608000&amp;date=20260626T004645Z&amp;version=1.0</t>
         </is>
       </c>
     </row>

--- a/weekly_temp/patents_量子软件与算法.xlsx
+++ b/weekly_temp/patents_量子软件与算法.xlsx
@@ -456,17 +456,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>系统</t>
+          <t>闭环量子比特校准技术</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>软银集团股份有限公司</t>
+          <t>英特尔公司</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>北山 翔平</t>
+          <t>수브라마니안, 수실 | 레빙거, 런 | 슈마커, 에브게니</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -476,42 +476,34 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>我们提供系统。 
- [解决方案] 
-一种利用放置在家庭环境中的录音设备来收集儿童行为信息的方法, 
-一种利用智能模型分析已收集到的各种信息来评估儿童发展特征的方法; 
-根据评估结果,提出一种促进儿童教育和发展的建议方法, 
-一种分析儿童情绪状态并根据需要提供即时报告的方法, 
-一种通过持续的数据积累来预测发育模式并及早发现潜在发育挑战的方法, 
-一种利用移动自主设备监测儿童活动并提供互动式教育体验的方法, 
-该系统包括根据分析结果向家长提供即时反馈并推荐个性化育儿方法的手段。</t>
+          <t>本文公开了一种用于控制自旋量子比特的脉冲闭环校准技术。在一个示例性实施例中,校准电路利用脉冲发生器产生脉冲。这些脉冲通过一个由滤波器参数控制的可变滤波器。脉冲被施加到量子比特上,并对其进行测量。根据测量得到的量子比特状态,可以改变滤波器参数。这样,​​就可以快速连续地校准控制脉冲。该校准方法具有多项优势。它可以由靠近物理量子比特的电路实现,从而降低噪声、串扰等干扰的可能性。该校准方法具有可扩展性,因为可以对给定的量子比特快速连续地进行校准,并且同一个校准电路可以复用以与多个量子比特连接。校准电路可以位于集成电路上,该集成电路可以位于量子计算机的低温级内。</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://analytics.zhihuiya.com/patent-view/abst?patentId=f36cf315-d771-4bd4-bd79-851b2461e788&amp;shareId=198G292E-EE74-750G-3C47-5E63C2EB5B01&amp;from=EXPORT&amp;signature=aPG1NpV1V4CDLw5vBIOMLwos9FU5AfJFQu6bhMP%2BD9c%3D&amp;expire=94608000&amp;date=20260626T004645Z&amp;version=1.0</t>
+          <t>https://analytics.zhihuiya.com/patent-view/abst?patentId=33a6ba33-ee84-4c24-ad07-0c2ca5864d0c&amp;shareId=8B1783G8-465F-516C-13FB-DB9D78C5GBBB&amp;from=EXPORT&amp;signature=3uyzxDTyo22VGeOOajQR%2FYfX%2BZCLHVSYADksKtOqmzw%3D&amp;expire=94608000&amp;date=20260710T003153Z&amp;version=1.0</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>系统</t>
+          <t>大型语言模型和量子计算机融合计算系统</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>软银集团股份有限公司</t>
+          <t>INTELLECTURE FUTURE IP MANAGEMENT CO LTD</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>鈴木 貴雄</t>
+          <t>안범주</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -521,261 +513,239 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>我们提供系统。 
- [解决方案] 
-收集和分析多语言信息的方法, 
-一种利用生成算法设计新的标准表示的方法, 
-将多语言信息转换为标准化表达并进行压缩的方法
-一种利用转换后的信息优化预测模型的方法, 
-一种利用预测模型与用户进行双向通信的方法, 
-一种实时呈现翻译信息的方式, 
-包含此功能的系统。</t>
+          <t>本发明涉及一种混合人工智能-量子计算系统,其中大型语言模型(LLM)将自然语言描述的高维优化问题转换为数学参数模型,量子计算机求解转换后的模型,LLM 将结果重新解释为自然语言文档。本发明包括规划器语言模型模块(110)、量子计算核心模块(120)、约束一致性检查器(130)、重新解释算法模块(140)、解释器语言模型模块(150)和双向跟踪表(160),并实现了一个端到端的跟踪链,其中分配给自然语言输入中各个约束的唯一标识符统一跟踪流水线的所有阶段,从QUBO术语、量子候选解、约束满足性判定到最终文档句子。这可以防止由LLM幻觉和NISQ量子误差引起的约束遗漏,定量地吸收关于多个候选解的不确定性,并为异构量子硬件平台提供平台独立性。</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://analytics.zhihuiya.com/patent-view/abst?patentId=05206804-f180-4003-a513-4128990ff3d7&amp;shareId=198G292E-EE74-750G-3C47-5E63C2EB5B01&amp;from=EXPORT&amp;signature=mX%2F6Si8MtE3gzweHffnMsOY2wPMMXXMimxAnhfRn2dk%3D&amp;expire=94608000&amp;date=20260626T004645Z&amp;version=1.0</t>
+          <t>https://analytics.zhihuiya.com/patent-view/abst?patentId=bfc677a3-51a0-4b8e-b9db-616a8863df2d&amp;shareId=8B1783G8-465F-516C-13FB-DB9D78C5GBBB&amp;from=EXPORT&amp;signature=C9iIL4U552u9SsDk9U0su2u1lw3fNClu%2BGEFRDMjAZI%3D&amp;expire=94608000&amp;date=20260710T003153Z&amp;version=1.0</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>制造量子器件的方法</t>
+          <t>用于量子化学系统的数据处理方法和装置</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>富士通株式会社</t>
+          <t>北京有竹居网络技术有限公司</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>MIYATAKE, TETSUYA</t>
+          <t>REN, WEILUO | CHAI, CHENLIN | FU, WEIZHONG | CHEN, JI</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>公开专利</t>
+          <t>授权专利</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>一种制造量子器件(100、200)的方法,包括:将包括色心(21)的金刚石衬底(30)键合到设置在支撑衬底(10)上的层(32);在键合金刚石衬底之后,通过蚀刻金刚石衬底形成包括色心的第一部分(40)和具有相对于第一部分的侧壁(41)倾斜的倾斜表面(43)的第二部分(42);在倾斜表面上形成金属膜(45);以及通过将由金属膜反射的激光束发射到第一部分的侧壁上,在比色心更远离层的第一位置处切割第一部分,形成第一光波导部分(20)。</t>
+          <t>本公开涉及一种量子化学体系的数据处理方法及装置。该量子化学体系的数据处理方法包括以下步骤:获取基于神经网络构建的、适用于量子化学体系的特定波函数;基于所述特定波函数进行游走子处理,所述游走子处理包括游走子的扩散处理;基于所述特定波函数及处理后的游走子,确定量子化学体系化学性质的相关信息。</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://analytics.zhihuiya.com/patent-view/abst?patentId=147d295d-d8ec-42f5-992e-6849a8347ea5&amp;shareId=198G292E-EE74-750G-3C47-5E63C2EB5B01&amp;from=EXPORT&amp;signature=1LRVFVPrGAVE63BzDm9n2Gd4dL4mu06NQBSQPD7%2FE3s%3D&amp;expire=94608000&amp;date=20260626T004645Z&amp;version=1.0</t>
+          <t>https://analytics.zhihuiya.com/patent-view/abst?patentId=141f5303-276a-46d7-bdaa-8dc7f3f6b2ce&amp;shareId=8B1783G8-465F-516C-13FB-DB9D78C5GBBB&amp;from=EXPORT&amp;signature=kA%2FHOBeeRsjxQGSAP%2FQxnlk5zbIfuC8IyWX6Jnox3IQ%3D&amp;expire=94608000&amp;date=20260710T003153Z&amp;version=1.0</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>将应用迁移到后量子密码术(PQC)状态的工作量的估计</t>
+          <t>用于制造与量子位的耦合的布置和方法</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>塔塔顾问服务有限公司</t>
+          <t>IQM芬兰有限公司</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>BHOWMICK, AMIT | VIDHANI, KUMAR MANSUKHLAL | ALASINGARA, BHATTACHAR</t>
+          <t>HEIMONEN, HERMANNI | LÄHTEENMÄKI, PASI</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>公开专利</t>
+          <t>授权专利</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>过去几十年来,准确估计完成应用迁移所需的代码行(LoC)的能力一直是一个挑战。本文公开的实施例提供了一种用于估计将应用迁移到后量子密码(PQC)状态的工作量的方法和系统。基于针对存在于精细分片输出和精细耦合输出中的一个或多个组件所确定的循环复杂度来估计该系统。此外,使用循环复杂度和受一个或多个密码API影响的LoC的数量来估计迁移的工作量。</t>
+          <t>一种用于与量子比特耦合的装置包括所述量子比特和另一电路元件,该电路元件可控地耦合到所述量子比特并与之解耦。在所述量子比特和所述另一电路元件之间设置有谐振器网络。所述谐振器网络包括多个谐振器,这些谐振器可以是线性谐振器、非线性谐振器或两者兼有。所述多个谐振器中至少有两个具有相同的电路拓扑结构,但频率响应不同。</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://analytics.zhihuiya.com/patent-view/abst?patentId=33c6710b-c21a-4984-bbe8-048106c16b2b&amp;shareId=198G292E-EE74-750G-3C47-5E63C2EB5B01&amp;from=EXPORT&amp;signature=Wap4suo%2BlI8eezOxtgJgww9rFAJGRuV8FW%2FcLrGzzts%3D&amp;expire=94608000&amp;date=20260626T004645Z&amp;version=1.0</t>
+          <t>https://analytics.zhihuiya.com/patent-view/abst?patentId=b6d5612d-1005-4786-ae91-83eb8beca65a&amp;shareId=8B1783G8-465F-516C-13FB-DB9D78C5GBBB&amp;from=EXPORT&amp;signature=VbBphn%2FCoMqSyG%2BE9M9%2FUsknDtMDQfcZhGlhh2MuWtQ%3D&amp;expire=94608000&amp;date=20260710T003153Z&amp;version=1.0</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>减少量子计算机中使用的量子位</t>
+          <t>用于改善量子位电路的功能的反熔丝和熔丝结构</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>微软技术许可有限责任公司</t>
+          <t>国际商业机器公司</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>SU, YUAN | KANG, CHRISTOPHER THOMAS</t>
+          <t>ADIGA, VIVEKANANDA | BUDD, RUSSELL | RETTNER, CHARLES | GATES, STEPHEN</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>公开专利</t>
+          <t>授权专利</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>本公开的各方面包括用于操作量子电路的过程。各方面包括利用单元演化对第一被乘数和第二被乘数执行哈密尔顿块编码,分别产生第一中间算子和第二中间算子。各方面包括对第一中间算子执行第一门和对第二中间算子执行第二门,分别产生修改的第一中间算子和修改的第二中间算子。各方面包括执行交换子积公式以组合修改的第一中间算子和修改的第二中间算子,产生组合算子,并且对组合算子执行另一第一门和另一第二门,产生修改的组合算子。另一第二门包括另一第一门的共轭转置。在量子电路上利用两个辅助量子位。</t>
+          <t>一种超导连接系统包含一个反熔丝结构。该系统包括第一超导走线,其第一段悬臂式地悬置于基板上的空腔上方。第二超导走线,其第二段悬臂式地悬置于基板上的空腔上方。第一辅助段与第一段耦合并悬置于空腔上方。第二辅助段与第二段耦合并悬置于空腔上方。第一段和第二段彼此相对,且二者之间具有预定的间隙。第一段和第二段配置成接收激光输出。第一辅助段和第二辅助段的部分材料用于形成熔丝球接头,该熔丝球接头在接收激光输出时,可在第一超导走线和第二超导走线之间形成电短路。</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://analytics.zhihuiya.com/patent-view/abst?patentId=99cacae8-3277-48aa-bcd5-40b7bc9556c9&amp;shareId=198G292E-EE74-750G-3C47-5E63C2EB5B01&amp;from=EXPORT&amp;signature=HRm5nYt9eqUsmWz0RhgB6gBmUNjJzwQKKPPJWB%2BP1zQ%3D&amp;expire=94608000&amp;date=20260626T004645Z&amp;version=1.0</t>
+          <t>https://analytics.zhihuiya.com/patent-view/abst?patentId=66ec31b8-ffc6-4dab-a7e3-e465e6c12350&amp;shareId=8B1783G8-465F-516C-13FB-DB9D78C5GBBB&amp;from=EXPORT&amp;signature=Pf1rDk14%2F%2Fx25std%2B4lELFC0%2Bkm%2F7soyBm3Vg%2FPYpfo%3D&amp;expire=94608000&amp;date=20260710T003153Z&amp;version=1.0</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>量子点阵列的制造和有效接触各种栅极的方式</t>
+          <t>基于机器学习的量子噪声解码器</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>原子能和替代能源委员会</t>
+          <t>昆媞努姆有限責任公司</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>BERTRAND, BENOIT</t>
+          <t>メーガン·コハーゲン | ナタリー·クリスティン·ブラウン | シアラン·ライアン-アンダーソン</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>公开专利</t>
+          <t>授权专利</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>量子电子器件包括:- 用于容纳量子点的活性区域 (20),以及,- 紧贴该器件一个表面的:a) 多条网格线 (G11、G12、G13、G14),这些网格线彼此电隔离,并且每条网格线覆盖活性区域 (20) 的一部分;以及 b) 重建促进岛 (14-17、I4a-I7a),每条网格线上至少有一个岛,重建促进岛彼此间隔距离 (D1、D2、D3),每个重建促进岛包括一个侧翼,网格线的侧部 (P4-P7) 沿该侧翼延伸,该器件还包括至少一个电触点 (P4-P7),用于接触至少一条给定的网格线 (G11、G12、G13、G14)。至少一个电触点位于沿触点重建促进岛侧边延伸的给定网格线的侧面上(14-17,I4a-I7a)。</t>
+          <t>包括通过机器学习训练的量子错误判定模型的量子噪声解码器,使用包含基于特定量子处理器的操作而至少部分获取的经验操作数据的训练数据进行训练。基于通过机器学习训练的量子错误判定模型生成特定量子处理器的噪声模型。提供噪声模型。提供噪声模型包括以下至少一项:(a) 通过计算实体的显示器提供噪声模型的图形表示,使得特定量子处理器的组件或参数基于该图形表示被修改或改变;或者(b) 作为与由特定量子处理器的控制器或与控制器通信的计算实体执行的可执行指令相关联的输入来提供噪声模型,使得特定量子处理器的组件或参数基于该噪声模型被修改或改变。</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://analytics.zhihuiya.com/patent-view/abst?patentId=92bb9f73-0f44-40dc-b3b6-f7273088bdf1&amp;shareId=198G292E-EE74-750G-3C47-5E63C2EB5B01&amp;from=EXPORT&amp;signature=uBapswM4SNm755iLb%2FLWAbPS5zRkhGk5%2FKk2ude%2F9L4%3D&amp;expire=94608000&amp;date=20260626T004645Z&amp;version=1.0</t>
+          <t>https://analytics.zhihuiya.com/patent-view/abst?patentId=319839a2-acc4-4f5b-9f7b-b601c2c80ac4&amp;shareId=8B1783G8-465F-516C-13FB-DB9D78C5GBBB&amp;from=EXPORT&amp;signature=BBtj7IzwgWXp%2BhZmjIoM7lTUW580xcX1i7wIO79OFPU%3D&amp;expire=94608000&amp;date=20260710T003153Z&amp;version=1.0</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>系统</t>
+          <t>一种基于量子卷积神经网络的洋面云检测方法</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>软银集团股份有限公司</t>
+          <t>中国科学技术大学</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>五條 眞樹</t>
+          <t>王雨 | 孟子祥 | 应圣钢 | 官极 | 何润洪 | 黄鸣宇 | 崔国龙 | 薛向辉</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>公开专利</t>
+          <t>授权专利</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>我们提供系统。 
- [解决方案] 
-为了支持跨文化交流, 
-收集不同文化信息的方法
-一种利用自然语言处理技术分析用户输入以了解文化背景的方法
-一种根据分析结果制定合适的沟通策略的方法, 
-向用户展示生成策略的一种方式, 
-基于乘客文化背景的语音导览优化方法
-包含此功能的系统。</t>
+          <t>本发明公开了一种基于量子卷积神经网络的洋面云检测方法，涉及云检测技术领域，将各通道反射率值通过归一化映射处理后作为旋转门的角度输入到编码层中；对每个量子比特通过Rx和Ry门操作编码两个特征；相邻量子比特通过CZ门实现空间特征关联，模拟经典卷积的局部连接特性；对量子比特进行池化操作；通过多次测量卷积和池化操作后剩下的两个量子比特的状态，获取到两个量子比特的测量期望值，通过训练量子卷积神经网络进行云检测任务，具有更好的泛化能力和更少的参数量；受量子并行性驱动，单一量子卷积操作可同时作用于整个光谱维度，避免了经典CNN中逐通道串行计算的冗余步骤。</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://analytics.zhihuiya.com/patent-view/abst?patentId=6db73478-fd06-4259-907b-029fbe6fe32e&amp;shareId=198G292E-EE74-750G-3C47-5E63C2EB5B01&amp;from=EXPORT&amp;signature=goKIEMdPH0oyF7LWIV6ShkWi2LLkDhTR3t6KZbRyaAE%3D&amp;expire=94608000&amp;date=20260626T004645Z&amp;version=1.0</t>
+          <t>https://analytics.zhihuiya.com/patent-view/abst?patentId=5d104472-4064-4c1c-ba5c-cd95d6c7bd29&amp;shareId=8B1783G8-465F-516C-13FB-DB9D78C5GBBB&amp;from=EXPORT&amp;signature=wBj%2BFq2Fl7L4pw632spSZHh12bqzzMNq9z%2BnPESHLmI%3D&amp;expire=94608000&amp;date=20260710T003153Z&amp;version=1.0</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>系统</t>
+          <t>一种基于互感调节与结不对称补偿的退相干时间提升方法</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>软银集团股份有限公司</t>
+          <t>北京工业大学</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>松崎 達彦</t>
+          <t>赵艳军 | 杨铮 | 高凤基</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>公开专利</t>
+          <t>授权专利</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>我们提供系统。 
- [解决方案] 
-一种利用自然语言处理算法分析电子邮件正文,并从中提取预定信息元素的方法; 
-一种基于提取的信息元素自动生成电子邮件主题行的方法, 
-一种利用生成式人工智能模型生成与电子支付等事件相关的电子邮件主题行的方法, 
-一种在移动信息终端设备的用户界面上显示生成的电子邮件主题的方法, 
-包含此功能的系统。</t>
+          <t>本发明提供了一种基于互感调节与结不对称补偿的退相干时间提升方法，属于超导量子计算技术领域。该方法包括：构建包含非平衡互感与非对称约瑟夫森结的超导量子比特理论模型；明确双结超导量子比特核心基础参数与约束条件，推导互感平衡补偿条件，调节磁通线接地电位置，改变左右两臂的互感的数值关系，消除互感不平衡引发的弛豫；定义结不对称参数与互感不平衡度，推导弛豫补偿条件，使互感不平衡引发的弛豫与结不对称引发的弛豫相互抵消，提升超导量子比特退相干时间。本发明建立了互感调节与结不对称补偿的定量关系，利用互感不平衡与结不对称的相互作用实现弛豫抵消，显著提升了量子比特的退相干时间与门保真度。</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://analytics.zhihuiya.com/patent-view/abst?patentId=61040822-06cc-4bc7-ac72-f5d29ba20241&amp;shareId=198G292E-EE74-750G-3C47-5E63C2EB5B01&amp;from=EXPORT&amp;signature=GmrQFBGaBjPoMklYAlWW6mwoDp5U6B97cTe2leqt55A%3D&amp;expire=94608000&amp;date=20260626T004645Z&amp;version=1.0</t>
+          <t>https://analytics.zhihuiya.com/patent-view/abst?patentId=3915ec6d-df84-430a-ac46-b13e060bf5b6&amp;shareId=8B1783G8-465F-516C-13FB-DB9D78C5GBBB&amp;from=EXPORT&amp;signature=gTLOP47VWtP5wAuVrwAX%2FLY0x5ie%2BRHApumDcsN%2FqxA%3D&amp;expire=94608000&amp;date=20260710T003153Z&amp;version=1.0</t>
         </is>
       </c>
     </row>

--- a/weekly_temp/patents_量子软件与算法.xlsx
+++ b/weekly_temp/patents_量子软件与算法.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G9"/>
+  <dimension ref="A1:G7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -456,91 +456,91 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>闭环量子比特校准技术</t>
+          <t>用于欺诈检测的图衍生特征</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>英特尔公司</t>
+          <t>PINDROP SECURITY INC</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>수브라마니안, 수실 | 레빙거, 런 | 슈마커, 에브게니</t>
+          <t>CASAL, RICARDO | WALKER, THEO | PATIL, KAILASH | CORNWELL, JOHN</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>公开专利</t>
+          <t>授权专利</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>本文公开了一种用于控制自旋量子比特的脉冲闭环校准技术。在一个示例性实施例中,校准电路利用脉冲发生器产生脉冲。这些脉冲通过一个由滤波器参数控制的可变滤波器。脉冲被施加到量子比特上,并对其进行测量。根据测量得到的量子比特状态,可以改变滤波器参数。这样,​​就可以快速连续地校准控制脉冲。该校准方法具有多项优势。它可以由靠近物理量子比特的电路实现,从而降低噪声、串扰等干扰的可能性。该校准方法具有可扩展性,因为可以对给定的量子比特快速连续地进行校准,并且同一个校准电路可以复用以与多个量子比特连接。校准电路可以位于集成电路上,该集成电路可以位于量子计算机的低温级内。</t>
+          <t>本文所述实施例提供了一种利用用户交互的图论特征进行风险评估的方法。计算机接收交互信息,并基于用于传输交互信息的通信信道提供给计算机的信息,从交互中推断出其他信息。计算机可以确定与用户交互关联的用户身份。计算机可以从推断出的身份和声称的身份中提取特征。计算机生成一个图,该图表示与推断出的身份和声称的身份关联的通信信道和声称的身份之间的结构关系。计算机可以使用该图从推断出的身份和声称的身份中提取其他特征。计算机可以将这些特征应用于机器学习模型,以生成风险评分,该评分指示与用户交互相关的欺诈交互的概率。</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://analytics.zhihuiya.com/patent-view/abst?patentId=33a6ba33-ee84-4c24-ad07-0c2ca5864d0c&amp;shareId=8B1783G8-465F-516C-13FB-DB9D78C5GBBB&amp;from=EXPORT&amp;signature=3uyzxDTyo22VGeOOajQR%2FYfX%2BZCLHVSYADksKtOqmzw%3D&amp;expire=94608000&amp;date=20260710T003153Z&amp;version=1.0</t>
+          <t>https://analytics.zhihuiya.com/patent-view/abst?patentId=bbb9819a-a0d6-42af-9dcd-29d55e3aa4b5&amp;shareId=30BBFD42-6G57-990D-0D80-12717CG13726&amp;from=EXPORT&amp;signature=d%2FcMsiQwRYYIA91fkc1fxItQJ0AUbhPn3bKA9UlnrMI%3D&amp;expire=94608000&amp;date=20260717T011438Z&amp;version=1.0</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>大型语言模型和量子计算机融合计算系统</t>
+          <t>用于分割多量子位可观测量的程序、用于分割多量子位可观测量的方法以及信息处理设备</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>INTELLECTURE FUTURE IP MANAGEMENT CO LTD</t>
+          <t>富士通株式会社</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>안범주</t>
+          <t>KURITA, TOMOCHIKA</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>公开专利</t>
+          <t>授权专利</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>本发明涉及一种混合人工智能-量子计算系统,其中大型语言模型(LLM)将自然语言描述的高维优化问题转换为数学参数模型,量子计算机求解转换后的模型,LLM 将结果重新解释为自然语言文档。本发明包括规划器语言模型模块(110)、量子计算核心模块(120)、约束一致性检查器(130)、重新解释算法模块(140)、解释器语言模型模块(150)和双向跟踪表(160),并实现了一个端到端的跟踪链,其中分配给自然语言输入中各个约束的唯一标识符统一跟踪流水线的所有阶段,从QUBO术语、量子候选解、约束满足性判定到最终文档句子。这可以防止由LLM幻觉和NISQ量子误差引起的约束遗漏,定量地吸收关于多个候选解的不确定性,并为异构量子硬件平台提供平台独立性。</t>
+          <t>减少了分割过程中生成的团数。信息处理设备 (10) 使用伊辛机 (1) 生成第一团 (4),该第一团表示可观测量的组合,该组合位于多个可观测量的第一组 (3) 中,并且可同时测量其预期值。信息处理设备 (10) 生成第二组 (5),该第二组包含可与第一团 (4) 中的可观测量同时测量预期值的可观测量。信息处理设备 (10) 使用伊辛机 (1) 生成第二团 (6),该第二团表示可观测量的组合,该组合位于第一团 (4) 和第二组 (5) 的并集 (7) 中,并且可同时测量其预期值。然后,信息处理设备(10)基于第一团(4)重复生成第二团(6),并使用第二团(6)中包含的可观测量进行更新,直到满足结束条件。</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://analytics.zhihuiya.com/patent-view/abst?patentId=bfc677a3-51a0-4b8e-b9db-616a8863df2d&amp;shareId=8B1783G8-465F-516C-13FB-DB9D78C5GBBB&amp;from=EXPORT&amp;signature=C9iIL4U552u9SsDk9U0su2u1lw3fNClu%2BGEFRDMjAZI%3D&amp;expire=94608000&amp;date=20260710T003153Z&amp;version=1.0</t>
+          <t>https://analytics.zhihuiya.com/patent-view/abst?patentId=a1212a82-7ca9-4996-84d7-43b8043262be&amp;shareId=30BBFD42-6G57-990D-0D80-12717CG13726&amp;from=EXPORT&amp;signature=zTXG0YIaPDZ2YudopChaMU29UJrkeIw5FYKSTL5xodY%3D&amp;expire=94608000&amp;date=20260717T011438Z&amp;version=1.0</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>用于量子化学系统的数据处理方法和装置</t>
+          <t>量子测控参数的处理方法、装置、设备及存储介质</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>北京有竹居网络技术有限公司</t>
+          <t>北京百度网讯科技有限公司</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>REN, WEILUO | CHAI, CHENLIN | FU, WEIZHONG | CHEN, JI</t>
+          <t>孟则霖</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -550,34 +550,34 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>本公开涉及一种量子化学体系的数据处理方法及装置。该量子化学体系的数据处理方法包括以下步骤:获取基于神经网络构建的、适用于量子化学体系的特定波函数;基于所述特定波函数进行游走子处理,所述游走子处理包括游走子的扩散处理;基于所述特定波函数及处理后的游走子,确定量子化学体系化学性质的相关信息。</t>
+          <t>本公开提供了量子测控参数的处理方法、装置、设备及其存储介质，涉及数据处理领域，尤其涉及量子计算、超导量子计算、量子控制等技术领域。具体实现方案为：确定第一初始映射关系B2F，其中，所述第一初始映射关系B2F是对目标集合所包含的二元采样组进行拟合处理所得，能够表征量子比特的偏置值至量子比特的比特频率的映射关系；在确定第一初始映射关系B2F中包含有预设偏置值下的情况下，以及用于拟合的目标集合达到采样终止条件的情况下，基于目标集合所包含的各二元采样组，拟合得到目标映射关系B2F*；其中，目标映射关系B2F*用于表征量子比特的偏置值与量子比特的比特频率之间的映射关系。</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://analytics.zhihuiya.com/patent-view/abst?patentId=141f5303-276a-46d7-bdaa-8dc7f3f6b2ce&amp;shareId=8B1783G8-465F-516C-13FB-DB9D78C5GBBB&amp;from=EXPORT&amp;signature=kA%2FHOBeeRsjxQGSAP%2FQxnlk5zbIfuC8IyWX6Jnox3IQ%3D&amp;expire=94608000&amp;date=20260710T003153Z&amp;version=1.0</t>
+          <t>https://analytics.zhihuiya.com/patent-view/abst?patentId=32218791-5383-4352-a016-7cff3fb3988b&amp;shareId=30BBFD42-6G57-990D-0D80-12717CG13726&amp;from=EXPORT&amp;signature=K2MAUs0WuCVx8HU8qZvX5XDfqkyLXFmKm7cgy1OFjmY%3D&amp;expire=94608000&amp;date=20260717T011438Z&amp;version=1.0</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>用于制造与量子位的耦合的布置和方法</t>
+          <t>一种基于小波变换的高安全量子随机数发生器系统</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>IQM芬兰有限公司</t>
+          <t>中国电子科技集团公司第三十研究所</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>HEIMONEN, HERMANNI | LÄHTEENMÄKI, PASI</t>
+          <t>杨杰 | 徐兵杰 | 刘龙举 | 吴梅 | 李扬 | 黄伟 | 高羽</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -587,34 +587,34 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>一种用于与量子比特耦合的装置包括所述量子比特和另一电路元件,该电路元件可控地耦合到所述量子比特并与之解耦。在所述量子比特和所述另一电路元件之间设置有谐振器网络。所述谐振器网络包括多个谐振器,这些谐振器可以是线性谐振器、非线性谐振器或两者兼有。所述多个谐振器中至少有两个具有相同的电路拓扑结构,但频率响应不同。</t>
+          <t>本发明涉及量子随机数发生器领域，提供一种基于小波变换的高安全量子随机数发生器系统，包括原始随机序列产生模块以及与所述原始随机序列产生模块连接的安全监测模块和后处理与随机性检测模块；所述原始随机序列产生模块，用于产生原始随机序列；所述安全监测模块，用于基于小波变换对所述原始随机序列进行处理，以判断系统是否存在异常；所述后处理与随机性检测模块，用于在系统不存在异常时对所述原始随机序列进行后处理与随机性检测。本发明通过实时监测和异常检测，显著提高了对信号异常和潜在攻击的识别能力，并利用小波变换进行时频分析，使得系统能够精确捕捉信号的局部变化，增强了安全性。</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://analytics.zhihuiya.com/patent-view/abst?patentId=b6d5612d-1005-4786-ae91-83eb8beca65a&amp;shareId=8B1783G8-465F-516C-13FB-DB9D78C5GBBB&amp;from=EXPORT&amp;signature=VbBphn%2FCoMqSyG%2BE9M9%2FUsknDtMDQfcZhGlhh2MuWtQ%3D&amp;expire=94608000&amp;date=20260710T003153Z&amp;version=1.0</t>
+          <t>https://analytics.zhihuiya.com/patent-view/abst?patentId=dabe7d1e-4d65-469a-a71a-fdce6abc5533&amp;shareId=30BBFD42-6G57-990D-0D80-12717CG13726&amp;from=EXPORT&amp;signature=VRJPf7AzwdWioyn2VT3FLc7NIyGEntVK8p2nlUiybN0%3D&amp;expire=94608000&amp;date=20260717T011438Z&amp;version=1.0</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>用于改善量子位电路的功能的反熔丝和熔丝结构</t>
+          <t>一种超流氦中量子涡旋的精确调控装置及方法</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>国际商业机器公司</t>
+          <t>浙江大学</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>ADIGA, VIVEKANANDA | BUDD, RUSSELL | RETTNER, CHARLES | GATES, STEPHEN</t>
+          <t>包士然 | 胡应璇 | 黄雯琳 | 骆科旭 | 邱利民</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -624,34 +624,34 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>一种超导连接系统包含一个反熔丝结构。该系统包括第一超导走线,其第一段悬臂式地悬置于基板上的空腔上方。第二超导走线,其第二段悬臂式地悬置于基板上的空腔上方。第一辅助段与第一段耦合并悬置于空腔上方。第二辅助段与第二段耦合并悬置于空腔上方。第一段和第二段彼此相对,且二者之间具有预定的间隙。第一段和第二段配置成接收激光输出。第一辅助段和第二辅助段的部分材料用于形成熔丝球接头,该熔丝球接头在接收激光输出时,可在第一超导走线和第二超导走线之间形成电短路。</t>
+          <t>本发明公开了一种超流氦中量子涡旋的精确调控装置及方法，包括：低温制取与维持系统，包括压缩机、冷水机组、制冷机冷头和液氦室，用于对氦气进行冷却与液化；屏蔽与真空系统，包括真空腔室冷屏、77 K冷屏和4 K冷屏；压力与抽排系统，包括观察室的减压抽空口、减压蝶阀与减压泵组，用于对观察室进行抽排与减压控制；观察与执行单元，包括具有视窗的观察室、布置于观察室内的加热器、由电机驱动的运动格栅、示踪粒子或氦气的注入口以及高速相机；控制系统，与上述各系统电连接并用于协同控制与数据采集。本发明能够在可控低温环境下实现对量子涡旋生成、演化及空间分布进行精确调控与实时观测。</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://analytics.zhihuiya.com/patent-view/abst?patentId=66ec31b8-ffc6-4dab-a7e3-e465e6c12350&amp;shareId=8B1783G8-465F-516C-13FB-DB9D78C5GBBB&amp;from=EXPORT&amp;signature=Pf1rDk14%2F%2Fx25std%2B4lELFC0%2Bkm%2F7soyBm3Vg%2FPYpfo%3D&amp;expire=94608000&amp;date=20260710T003153Z&amp;version=1.0</t>
+          <t>https://analytics.zhihuiya.com/patent-view/abst?patentId=328a8ac1-96bf-45f2-a59b-be5d5e70abb3&amp;shareId=30BBFD42-6G57-990D-0D80-12717CG13726&amp;from=EXPORT&amp;signature=ohpMQ2g4QO%2FFDplTnIYftBnNlEJOofh3TyW1B9E0nak%3D&amp;expire=94608000&amp;date=20260717T011438Z&amp;version=1.0</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>基于机器学习的量子噪声解码器</t>
+          <t>基于光量子的非线性数据生成和处理方法及光量子计算机</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>昆媞努姆有限責任公司</t>
+          <t>上海图灵智算量子科技有限公司</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>メーガン·コハーゲン | ナタリー·クリスティン·ブラウン | シアラン·ライアン-アンダーソン</t>
+          <t>朱宇泽 | 何俊杰 | 胡克明 | 杨林</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -661,91 +661,17 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>包括通过机器学习训练的量子错误判定模型的量子噪声解码器,使用包含基于特定量子处理器的操作而至少部分获取的经验操作数据的训练数据进行训练。基于通过机器学习训练的量子错误判定模型生成特定量子处理器的噪声模型。提供噪声模型。提供噪声模型包括以下至少一项:(a) 通过计算实体的显示器提供噪声模型的图形表示,使得特定量子处理器的组件或参数基于该图形表示被修改或改变;或者(b) 作为与由特定量子处理器的控制器或与控制器通信的计算实体执行的可执行指令相关联的输入来提供噪声模型,使得特定量子处理器的组件或参数基于该噪声模型被修改或改变。</t>
+          <t>本申请提供了一种基于光量子的非线性数据生成和处理方法及光量子计算机，其中，该方法包括：获取非线性层的非线性函数以及属性信息；根据非线性函数的频谱数量以及属性信息，构造初始光量子线路；对初始光量子线路进行测量，根据测量结果确定初始光量子线路对应的目标函数；确定目标函数的损失信息，根据损失信息确定是否应用初始光量子线路，若是，则将初始光量子线路作为目标光量子线路；基于目标光量子线路对非线性层的输入数据进行运算。本申请能够融合光子计算的低能耗特性、光量子计算的非线性特性以及电子计算的通用可编程能力，对非线性层的输入数据高能效计算。此外，还具备量子线路复杂度更小，且不需要非线性光学器件的参与的优点。</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://analytics.zhihuiya.com/patent-view/abst?patentId=319839a2-acc4-4f5b-9f7b-b601c2c80ac4&amp;shareId=8B1783G8-465F-516C-13FB-DB9D78C5GBBB&amp;from=EXPORT&amp;signature=BBtj7IzwgWXp%2BhZmjIoM7lTUW580xcX1i7wIO79OFPU%3D&amp;expire=94608000&amp;date=20260710T003153Z&amp;version=1.0</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>一种基于量子卷积神经网络的洋面云检测方法</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>中国科学技术大学</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>王雨 | 孟子祥 | 应圣钢 | 官极 | 何润洪 | 黄鸣宇 | 崔国龙 | 薛向辉</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>授权专利</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>2026-07-07</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>本发明公开了一种基于量子卷积神经网络的洋面云检测方法，涉及云检测技术领域，将各通道反射率值通过归一化映射处理后作为旋转门的角度输入到编码层中；对每个量子比特通过Rx和Ry门操作编码两个特征；相邻量子比特通过CZ门实现空间特征关联，模拟经典卷积的局部连接特性；对量子比特进行池化操作；通过多次测量卷积和池化操作后剩下的两个量子比特的状态，获取到两个量子比特的测量期望值，通过训练量子卷积神经网络进行云检测任务，具有更好的泛化能力和更少的参数量；受量子并行性驱动，单一量子卷积操作可同时作用于整个光谱维度，避免了经典CNN中逐通道串行计算的冗余步骤。</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>https://analytics.zhihuiya.com/patent-view/abst?patentId=5d104472-4064-4c1c-ba5c-cd95d6c7bd29&amp;shareId=8B1783G8-465F-516C-13FB-DB9D78C5GBBB&amp;from=EXPORT&amp;signature=wBj%2BFq2Fl7L4pw632spSZHh12bqzzMNq9z%2BnPESHLmI%3D&amp;expire=94608000&amp;date=20260710T003153Z&amp;version=1.0</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>一种基于互感调节与结不对称补偿的退相干时间提升方法</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>北京工业大学</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>赵艳军 | 杨铮 | 高凤基</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>授权专利</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>2026-07-07</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>本发明提供了一种基于互感调节与结不对称补偿的退相干时间提升方法，属于超导量子计算技术领域。该方法包括：构建包含非平衡互感与非对称约瑟夫森结的超导量子比特理论模型；明确双结超导量子比特核心基础参数与约束条件，推导互感平衡补偿条件，调节磁通线接地电位置，改变左右两臂的互感的数值关系，消除互感不平衡引发的弛豫；定义结不对称参数与互感不平衡度，推导弛豫补偿条件，使互感不平衡引发的弛豫与结不对称引发的弛豫相互抵消，提升超导量子比特退相干时间。本发明建立了互感调节与结不对称补偿的定量关系，利用互感不平衡与结不对称的相互作用实现弛豫抵消，显著提升了量子比特的退相干时间与门保真度。</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>https://analytics.zhihuiya.com/patent-view/abst?patentId=3915ec6d-df84-430a-ac46-b13e060bf5b6&amp;shareId=8B1783G8-465F-516C-13FB-DB9D78C5GBBB&amp;from=EXPORT&amp;signature=gTLOP47VWtP5wAuVrwAX%2FLY0x5ie%2BRHApumDcsN%2FqxA%3D&amp;expire=94608000&amp;date=20260710T003153Z&amp;version=1.0</t>
+          <t>https://analytics.zhihuiya.com/patent-view/abst?patentId=f0a14708-b741-4913-a2b0-4ab7e821c8f9&amp;shareId=30BBFD42-6G57-990D-0D80-12717CG13726&amp;from=EXPORT&amp;signature=qJcKFrONYdCdoRtMQ4%2BUvNKtbxktOQwkqHK1eSaGV0Q%3D&amp;expire=94608000&amp;date=20260717T011438Z&amp;version=1.0</t>
         </is>
       </c>
     </row>

--- a/weekly_temp/patents_量子软件与算法.xlsx
+++ b/weekly_temp/patents_量子软件与算法.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G7"/>
+  <dimension ref="A1:G9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -456,17 +456,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>用于欺诈检测的图衍生特征</t>
+          <t>量子控制系统的路由装置、方法以及量子计算机</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>PINDROP SECURITY INC</t>
+          <t>本源量子计算科技(合肥)股份有限公司</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>CASAL, RICARDO | WALKER, THEO | PATIL, KAILASH | CORNWELL, JOHN</t>
+          <t>李雪白</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -476,34 +476,34 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>本文所述实施例提供了一种利用用户交互的图论特征进行风险评估的方法。计算机接收交互信息,并基于用于传输交互信息的通信信道提供给计算机的信息,从交互中推断出其他信息。计算机可以确定与用户交互关联的用户身份。计算机可以从推断出的身份和声称的身份中提取特征。计算机生成一个图,该图表示与推断出的身份和声称的身份关联的通信信道和声称的身份之间的结构关系。计算机可以使用该图从推断出的身份和声称的身份中提取其他特征。计算机可以将这些特征应用于机器学习模型,以生成风险评分,该评分指示与用户交互相关的欺诈交互的概率。</t>
+          <t>本申请提供了一种量子控制系统的路由装置，包括：路由配置模块，其被配置为接收并转发待执行的量子计算任务的数据包，其中，所述数据包包括任务编号、以及对应的任务数据；中控转发模块，其被配置为转发中控模块的第一触发信号，其中，所述第一触发信号为所述中控模块响应就绪信号输出的信号，所述就绪信号为功能模块配置所述任务数据后输出的信号；多个路由触发模块，每个所述路由触发模块被配置为接收一个任务编号对应的任务数据，并根据接收到的所述第一触发信号输出第二触发信号，其中，所述第二触发信号用于触发功能模块依据所述任务数据输出用于量子位的驱动信号。本申请能够提高量子控制系统的运行效率。</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://analytics.zhihuiya.com/patent-view/abst?patentId=bbb9819a-a0d6-42af-9dcd-29d55e3aa4b5&amp;shareId=30BBFD42-6G57-990D-0D80-12717CG13726&amp;from=EXPORT&amp;signature=d%2FcMsiQwRYYIA91fkc1fxItQJ0AUbhPn3bKA9UlnrMI%3D&amp;expire=94608000&amp;date=20260717T011438Z&amp;version=1.0</t>
+          <t>https://analytics.zhihuiya.com/patent-view/abst?patentId=b59093a1-30d0-4c81-abbe-958d1e97d930&amp;shareId=61CD4199-4E7B-7C36-C999-3CEDB31E0762&amp;from=EXPORT&amp;signature=h285IRxLFWNIMpM5ipNTP81sXR5%2FrWOZmOA8fK0nKQ0%3D&amp;expire=94608000&amp;date=20260821T055613Z&amp;version=1.0</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>用于分割多量子位可观测量的程序、用于分割多量子位可观测量的方法以及信息处理设备</t>
+          <t>量子比特之间耦合关系的控制方法、装置以及量子计算机</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>富士通株式会社</t>
+          <t>本源量子计算科技(合肥)股份有限公司</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>KURITA, TOMOCHIKA</t>
+          <t>请求不公布姓名 | 孔伟成</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -513,34 +513,34 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>减少了分割过程中生成的团数。信息处理设备 (10) 使用伊辛机 (1) 生成第一团 (4),该第一团表示可观测量的组合,该组合位于多个可观测量的第一组 (3) 中,并且可同时测量其预期值。信息处理设备 (10) 生成第二组 (5),该第二组包含可与第一团 (4) 中的可观测量同时测量预期值的可观测量。信息处理设备 (10) 使用伊辛机 (1) 生成第二团 (6),该第二团表示可观测量的组合,该组合位于第一团 (4) 和第二组 (5) 的并集 (7) 中,并且可同时测量其预期值。然后,信息处理设备(10)基于第一团(4)重复生成第二团(6),并使用第二团(6)中包含的可观测量进行更新,直到满足结束条件。</t>
+          <t>本发明公开了一种量子比特之间耦合关系的控制方法、装置以及量子计算机，利用本申请的方案可有效降低用于执行两量子比特逻辑门的第一量子比特与第二量子比特之间的耦合强度，并且降低了与量子芯片中邻近的量子比特也即第三量子比特的耦合强度，有效提高两量子比特逻辑门执行准确度，在一定程度上提高了量子计算机的执行精确性。</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://analytics.zhihuiya.com/patent-view/abst?patentId=a1212a82-7ca9-4996-84d7-43b8043262be&amp;shareId=30BBFD42-6G57-990D-0D80-12717CG13726&amp;from=EXPORT&amp;signature=zTXG0YIaPDZ2YudopChaMU29UJrkeIw5FYKSTL5xodY%3D&amp;expire=94608000&amp;date=20260717T011438Z&amp;version=1.0</t>
+          <t>https://analytics.zhihuiya.com/patent-view/abst?patentId=bf683a25-4ff0-40ca-9da2-6b5966e4fc89&amp;shareId=61CD4199-4E7B-7C36-C999-3CEDB31E0762&amp;from=EXPORT&amp;signature=TUVhxL5bl16LMagOu%2F5VPRAcrD7uydbO4I1WAW%2BbSc0%3D&amp;expire=94608000&amp;date=20260821T055613Z&amp;version=1.0</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>量子测控参数的处理方法、装置、设备及存储介质</t>
+          <t>基于计算机视觉的超导量子芯片版图组件自动化识别与提取方法</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>北京百度网讯科技有限公司</t>
+          <t>中国人民解放军网络空间部队信息工程大学</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>孟则霖</t>
+          <t>单征 | 万仞山 | 于小涵 | 赵博 | 戚旭衍 | 李志航 | 刘福东 | 孙回回 | 穆清 | 王淑亚 | 王卫龙 | 马芯宇 | 袁本政 | 赵炳麟 | 焦宇 | 韩传兵 | 张潮洁 | 徐鹏 | 王文青 | 陈正宇 | 安康 | 高翊闵 | 查治国</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -550,34 +550,34 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>本公开提供了量子测控参数的处理方法、装置、设备及其存储介质，涉及数据处理领域，尤其涉及量子计算、超导量子计算、量子控制等技术领域。具体实现方案为：确定第一初始映射关系B2F，其中，所述第一初始映射关系B2F是对目标集合所包含的二元采样组进行拟合处理所得，能够表征量子比特的偏置值至量子比特的比特频率的映射关系；在确定第一初始映射关系B2F中包含有预设偏置值下的情况下，以及用于拟合的目标集合达到采样终止条件的情况下，基于目标集合所包含的各二元采样组，拟合得到目标映射关系B2F*；其中，目标映射关系B2F*用于表征量子比特的偏置值与量子比特的比特频率之间的映射关系。</t>
+          <t>本公开的实施例公开了基于计算机视觉的超导量子芯片版图组件自动化识别与提取方法。该方法的一具体实施方式包括：对已读取的超导量子芯片版图进行版图解析，得到组件几何信息集合；对于组件几何信息集合中的每个组件几何信息，根据组件几何信息，生成组件几何信息对应芯片组件的芯片组件图；对得到的芯片组件图集合中的每张芯片组件图进行特征提取，以生成芯片组件图对应的图像描述特征；根据芯片组件图对应的图像描述特征进行芯片组件匹配，以生成芯片组件库。该实施方式显著提升设计效率，减少人工干预。</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://analytics.zhihuiya.com/patent-view/abst?patentId=32218791-5383-4352-a016-7cff3fb3988b&amp;shareId=30BBFD42-6G57-990D-0D80-12717CG13726&amp;from=EXPORT&amp;signature=K2MAUs0WuCVx8HU8qZvX5XDfqkyLXFmKm7cgy1OFjmY%3D&amp;expire=94608000&amp;date=20260717T011438Z&amp;version=1.0</t>
+          <t>https://analytics.zhihuiya.com/patent-view/abst?patentId=d65a5a52-ea69-41d5-8dfa-c29df156417e&amp;shareId=61CD4199-4E7B-7C36-C999-3CEDB31E0762&amp;from=EXPORT&amp;signature=GVtcBs%2FtkLCC5IRsyGliC9ppoQZ4i7nErCAHJTsvGSM%3D&amp;expire=94608000&amp;date=20260821T055613Z&amp;version=1.0</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>一种基于小波变换的高安全量子随机数发生器系统</t>
+          <t>波形处理方法、测控系统、量子计算机、介质和设备</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>中国电子科技集团公司第三十研究所</t>
+          <t>本源量子计算科技(合肥)股份有限公司</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>杨杰 | 徐兵杰 | 刘龙举 | 吴梅 | 李扬 | 黄伟 | 高羽</t>
+          <t>请求不公布姓名 | 孔伟成</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -587,34 +587,34 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>本发明涉及量子随机数发生器领域，提供一种基于小波变换的高安全量子随机数发生器系统，包括原始随机序列产生模块以及与所述原始随机序列产生模块连接的安全监测模块和后处理与随机性检测模块；所述原始随机序列产生模块，用于产生原始随机序列；所述安全监测模块，用于基于小波变换对所述原始随机序列进行处理，以判断系统是否存在异常；所述后处理与随机性检测模块，用于在系统不存在异常时对所述原始随机序列进行后处理与随机性检测。本发明通过实时监测和异常检测，显著提高了对信号异常和潜在攻击的识别能力，并利用小波变换进行时频分析，使得系统能够精确捕捉信号的局部变化，增强了安全性。</t>
+          <t>本申请提供了波形处理方法、测控系统、量子计算机、介质和设备，所述方法包括：接收传输波形指令和扫描数据；使用所述扫描数据处理所述传输波形指令，以得到多个输出波形指令；将所述输出波形指令编译成实际波形数据，所述实际波形数据用于在量子计算测控实验任务中对量子比特进行控制或者测量。本申请允许对扫描数据与传输波形指令进行分离传输处理，实现内存的压缩，在编译过程中，所占用的内存较少，能够显著改善内存不足问题，降低任务失败风险，促进量子计算测控实验任务顺利完成，简化波形拼接等操作，允许用户更自由、灵活地去定义实验过程，不仅压缩量子计算测控实验的传输数据量，还有利于解耦实验和硬件，实现跨平台的兼容性。</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://analytics.zhihuiya.com/patent-view/abst?patentId=dabe7d1e-4d65-469a-a71a-fdce6abc5533&amp;shareId=30BBFD42-6G57-990D-0D80-12717CG13726&amp;from=EXPORT&amp;signature=VRJPf7AzwdWioyn2VT3FLc7NIyGEntVK8p2nlUiybN0%3D&amp;expire=94608000&amp;date=20260717T011438Z&amp;version=1.0</t>
+          <t>https://analytics.zhihuiya.com/patent-view/abst?patentId=04421a75-2c47-4bb8-ab9e-d0027df4377f&amp;shareId=61CD4199-4E7B-7C36-C999-3CEDB31E0762&amp;from=EXPORT&amp;signature=mfEJLdZgcqEzDdK9HpaO4msJ8LLUIIsEwRdpWbtKue0%3D&amp;expire=94608000&amp;date=20260821T055613Z&amp;version=1.0</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>一种超流氦中量子涡旋的精确调控装置及方法</t>
+          <t>一种量子线路编译方法及相关装置</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>浙江大学</t>
+          <t>本源量子计算科技(合肥)股份有限公司</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>包士然 | 胡应璇 | 黄雯琳 | 骆科旭 | 邱利民</t>
+          <t>窦猛汉 | 请求不公布姓名</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -624,34 +624,34 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>本发明公开了一种超流氦中量子涡旋的精确调控装置及方法，包括：低温制取与维持系统，包括压缩机、冷水机组、制冷机冷头和液氦室，用于对氦气进行冷却与液化；屏蔽与真空系统，包括真空腔室冷屏、77 K冷屏和4 K冷屏；压力与抽排系统，包括观察室的减压抽空口、减压蝶阀与减压泵组，用于对观察室进行抽排与减压控制；观察与执行单元，包括具有视窗的观察室、布置于观察室内的加热器、由电机驱动的运动格栅、示踪粒子或氦气的注入口以及高速相机；控制系统，与上述各系统电连接并用于协同控制与数据采集。本发明能够在可控低温环境下实现对量子涡旋生成、演化及空间分布进行精确调控与实时观测。</t>
+          <t>本申请公开了一种量子线路编译方法及相关装置，属于量子计算技术领域，方法包括：将待编译的量子线路的结构与量子芯片的拓扑结构进行匹配，确定目标布局，所确定的目标布局至少使得一个两比特逻辑门作用在相连的物理比特上；确定目标布局对应的所有路由方式；基于由目标路径上量子逻辑门确定的目标分值和目标两比特逻辑门的作用的物理比特之间的距离，对所获得的所有路由方式进行评估，确定目标路由方式；基于所述目标路由方式和对应的目标布局，编译所述量子线路。应用本申请实施例，提高了编译结果的可靠性。</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://analytics.zhihuiya.com/patent-view/abst?patentId=328a8ac1-96bf-45f2-a59b-be5d5e70abb3&amp;shareId=30BBFD42-6G57-990D-0D80-12717CG13726&amp;from=EXPORT&amp;signature=ohpMQ2g4QO%2FFDplTnIYftBnNlEJOofh3TyW1B9E0nak%3D&amp;expire=94608000&amp;date=20260717T011438Z&amp;version=1.0</t>
+          <t>https://analytics.zhihuiya.com/patent-view/abst?patentId=b22eecb9-0475-4f66-b943-78bbc798537b&amp;shareId=61CD4199-4E7B-7C36-C999-3CEDB31E0762&amp;from=EXPORT&amp;signature=RiVi1gNKx2KqlOAlKXCPJS2GKIxMy402%2FBlDm6o71aU%3D&amp;expire=94608000&amp;date=20260821T055613Z&amp;version=1.0</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>基于光量子的非线性数据生成和处理方法及光量子计算机</t>
+          <t>一种基于硬件感知的量子任务智能调度系统</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>上海图灵智算量子科技有限公司</t>
+          <t>成都中微达信科技有限公司</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>朱宇泽 | 何俊杰 | 胡克明 | 杨林</t>
+          <t>孟则霖 | 王亚男 | 赵雷 | 冯泠越</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -661,17 +661,91 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>本申请提供了一种基于光量子的非线性数据生成和处理方法及光量子计算机，其中，该方法包括：获取非线性层的非线性函数以及属性信息；根据非线性函数的频谱数量以及属性信息，构造初始光量子线路；对初始光量子线路进行测量，根据测量结果确定初始光量子线路对应的目标函数；确定目标函数的损失信息，根据损失信息确定是否应用初始光量子线路，若是，则将初始光量子线路作为目标光量子线路；基于目标光量子线路对非线性层的输入数据进行运算。本申请能够融合光子计算的低能耗特性、光量子计算的非线性特性以及电子计算的通用可编程能力，对非线性层的输入数据高能效计算。此外，还具备量子线路复杂度更小，且不需要非线性光学器件的参与的优点。</t>
+          <t>本发明公开了一种基于硬件感知的量子任务智能调度系统，涉及量子技术领域，该系统包括硬件监控模块、特征提取模块、匹配优化模块和调度优化模块；所述硬件监控模块采集物理参数和构建瞬时状态矩阵；所述特征提取模块提取资源特征与噪声特征；所述匹配优化模块最大化计算处理目标量子系统的全局期望成功率；所述调度优化模块基于变化后的瞬时状态矩阵更新全局期望成功率和更新最优任务队列。本发明通过周期性地采集和记录物理量子比特的关键物理参数，并通过动态调整任务队列和实时优化期望成功率，使得量子系统能够根据硬件的实时状态进行调整，从而确保了在任务量和资源需求增加时，提高任务的成功率和系统的整体稳定性。</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://analytics.zhihuiya.com/patent-view/abst?patentId=f0a14708-b741-4913-a2b0-4ab7e821c8f9&amp;shareId=30BBFD42-6G57-990D-0D80-12717CG13726&amp;from=EXPORT&amp;signature=qJcKFrONYdCdoRtMQ4%2BUvNKtbxktOQwkqHK1eSaGV0Q%3D&amp;expire=94608000&amp;date=20260717T011438Z&amp;version=1.0</t>
+          <t>https://analytics.zhihuiya.com/patent-view/abst?patentId=54f19ad3-6630-4ad2-93d7-48ef94ba92ed&amp;shareId=61CD4199-4E7B-7C36-C999-3CEDB31E0762&amp;from=EXPORT&amp;signature=JwQqpOBuJtbdOmaNqcZ%2F0geSU0ba%2FEi8RXVawtNwQV4%3D&amp;expire=94608000&amp;date=20260821T055613Z&amp;version=1.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>量子随机数生成速率增强装置及方法</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>合肥国家实验室 | 中国科学技术大学</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>白冰 | 汤晨宇 | 吴佳颖 | 陈瀚深 | 聂友奇 | 刘乃乐 | 蒋一 | 张军 | 潘建伟</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>授权专利</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>本发明提供了一种量子随机数生成速率增强装置及方法，主要涉及量子信息技术领域。其中，该装置包括：量子熵源模块，用于生成第一量子随机模拟信号；模数转换模块，包括均衡滤波单元；模数转换模块用于：利用均衡滤波单元基于目标幅频响应特征对第一量子随机数字信号的功率谱密度进行平坦化处理，得到经滤波的第一量子随机数字信号；其中，均衡滤波单元加载有滤波系数，以使得均衡滤波单元的目标幅频响应特征与模拟链路的幅频响应特征相反，并使得经滤波的第一量子随机数字信号的信号总能量与初始的第一量子随机数字信号的信号总能量相等；处理模块，用于对经滤波的第一量子随机数字信号进行随机性提取处理，输出量子随机数序列。</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>https://analytics.zhihuiya.com/patent-view/abst?patentId=965d0b5c-4326-475f-8658-ca0743ae927b&amp;shareId=61CD4199-4E7B-7C36-C999-3CEDB31E0762&amp;from=EXPORT&amp;signature=74ZJa1lm17%2FCCzHp%2F8yP61%2FVLWKUojZ40%2FrM5OqjfkQ%3D&amp;expire=94608000&amp;date=20260821T055613Z&amp;version=1.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>光子的频域任意线性变换</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>利兰斯坦福初级大学董事会</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>BUDDHIRAJU, SIDDHARTH | DUTT, AVIK | MINKOV, MOMCHIL | WILLIAMSON, IAN A.D. | FAN, SHANHUI</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>授权专利</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>一个或多个光学谐振器依次耦合到光波导上。每个谐振器都包含一个相应的调制器。信号控制器配置为使用相应的复合电信号驱动每个调制器。每个复合电信号包含由一个或多个谐振器定义的频率梳的两个或多个频率分量。这种配置的结果是,波导输入端和输出端之间的输入输出关系是由复合电信号定义的线性变换,该线性变换以频率梳的频率为基。这种线性变换可以是互易的或非互易的,也可以是酉变换或非酉变换。</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>https://analytics.zhihuiya.com/patent-view/abst?patentId=eca76b41-9d2c-4c94-948c-fb1fb17da9dc&amp;shareId=61CD4199-4E7B-7C36-C999-3CEDB31E0762&amp;from=EXPORT&amp;signature=XPsNTOwpGZQ%2B9lmVGiWB5k4UNsx5zbBCj16vGadREf4%3D&amp;expire=94608000&amp;date=20260821T055613Z&amp;version=1.0</t>
         </is>
       </c>
     </row>

--- a/weekly_temp/patents_量子软件与算法.xlsx
+++ b/weekly_temp/patents_量子软件与算法.xlsx
@@ -456,165 +456,165 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>量子控制系统的路由装置、方法以及量子计算机</t>
+          <t>用于贝叶斯推断的混合量子-经典计算机,采用工程似然函数实现稳健的振幅估计</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>本源量子计算科技(合肥)股份有限公司</t>
+          <t>札帕塔运算股份有限公司</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>李雪白</t>
+          <t>WANG, GUOMING | KOH, ENSHAN DAX | JOHNSON, PETER D. | CAO, YUDONG | DALLAIRE-DEMERS, PIERRE-LUC</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>授权专利</t>
+          <t>公开专利</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>本申请提供了一种量子控制系统的路由装置，包括：路由配置模块，其被配置为接收并转发待执行的量子计算任务的数据包，其中，所述数据包包括任务编号、以及对应的任务数据；中控转发模块，其被配置为转发中控模块的第一触发信号，其中，所述第一触发信号为所述中控模块响应就绪信号输出的信号，所述就绪信号为功能模块配置所述任务数据后输出的信号；多个路由触发模块，每个所述路由触发模块被配置为接收一个任务编号对应的任务数据，并根据接收到的所述第一触发信号输出第二触发信号，其中，所述第二触发信号用于触发功能模块依据所述任务数据输出用于量子位的驱动信号。本申请能够提高量子控制系统的运行效率。</t>
+          <t>混合量子-经典(HQC)计算机利用现有的量子相干性,最大限度地提升噪声量子器件的采样能力,与VQE相比,显著减少了测量次数和运行时间。HQC计算机的灵感来源于量子计量学、相位估计以及最新的“α-VQE”方案,最终形成了一种对误差具有鲁棒性且无需辅助量子比特的通用公式。HQC计算机采用“工程似然函数”(ELF)进行贝叶斯推断。随着物理硬件从噪声中等规模量子计算机过渡到量子纠错量子计算机,ELF形式进一步增强了采样方面的量子优势。这项技术加速了许多量子算法的核心组件,其应用领域涵盖化学、材料、金融等诸多方面。</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://analytics.zhihuiya.com/patent-view/abst?patentId=b59093a1-30d0-4c81-abbe-958d1e97d930&amp;shareId=61CD4199-4E7B-7C36-C999-3CEDB31E0762&amp;from=EXPORT&amp;signature=h285IRxLFWNIMpM5ipNTP81sXR5%2FrWOZmOA8fK0nKQ0%3D&amp;expire=94608000&amp;date=20260821T055613Z&amp;version=1.0</t>
+          <t>https://analytics.zhihuiya.com/patent-view/abst?patentId=724774ae-d754-41fc-bb0c-b0b3dcad8082&amp;shareId=F2GF84E7-1GC8-8BEF-B765-D6399653BCG0&amp;from=EXPORT&amp;signature=7biYqFZmj%2FcSzcaKURqMTyBdBpSWhhGcEJKhIxW9wZk%3D&amp;expire=94608000&amp;date=20260828T063351Z&amp;version=1.0</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>量子比特之间耦合关系的控制方法、装置以及量子计算机</t>
+          <t>用于大容量车辆路径问题(CVRP)的混合经典-量子系统</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>本源量子计算科技(合肥)股份有限公司</t>
+          <t>尤尼西斯公司</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>请求不公布姓名 | 孔伟成</t>
+          <t>SINNO, SALVATORE | MOTT, ALAN | SAHOO, ARATI | FERNANDO D, ANTONIO DAUPHIN | THURAVAKKATH, SHRUTHI</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>授权专利</t>
+          <t>公开专利</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>本发明公开了一种量子比特之间耦合关系的控制方法、装置以及量子计算机，利用本申请的方案可有效降低用于执行两量子比特逻辑门的第一量子比特与第二量子比特之间的耦合强度，并且降低了与量子芯片中邻近的量子比特也即第三量子比特的耦合强度，有效提高两量子比特逻辑门执行准确度，在一定程度上提高了量子计算机的执行精确性。</t>
+          <t>用于改进车辆路径规划的混合经典-量子系统采用了遗传算法、模拟退火和量子退火的组合。该混合方法可以进一步探索容量受限车辆路径问题 (CVRP) 的解空间,从而确定改进的路径规划结果。首先对节点(即位置)进行聚类,然后通过遗传算法处理节点簇以确定潜在解。使用模拟退火对潜在解进行演化,生成演化解,每个解都包含演化节点簇。选择一个演化解。所选演化解的每个演化节点簇分别由量子退火器进行退火,以确定穿过演化节点簇的最佳路径。</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://analytics.zhihuiya.com/patent-view/abst?patentId=bf683a25-4ff0-40ca-9da2-6b5966e4fc89&amp;shareId=61CD4199-4E7B-7C36-C999-3CEDB31E0762&amp;from=EXPORT&amp;signature=TUVhxL5bl16LMagOu%2F5VPRAcrD7uydbO4I1WAW%2BbSc0%3D&amp;expire=94608000&amp;date=20260821T055613Z&amp;version=1.0</t>
+          <t>https://analytics.zhihuiya.com/patent-view/abst?patentId=22160571-9273-4db4-83cc-313b5fd9ba78&amp;shareId=F2GF84E7-1GC8-8BEF-B765-D6399653BCG0&amp;from=EXPORT&amp;signature=ctWXqXKP88wMLmZeEjtE825ODYCvi3TfOUaPH1cCET0%3D&amp;expire=94608000&amp;date=20260828T063351Z&amp;version=1.0</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>基于计算机视觉的超导量子芯片版图组件自动化识别与提取方法</t>
+          <t>用于求解数字-模拟量子计算中的优化问题的进化方法</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>中国人民解放军网络空间部队信息工程大学</t>
+          <t>KIPU QUANTUM GMBH</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>单征 | 万仞山 | 于小涵 | 赵博 | 戚旭衍 | 李志航 | 刘福东 | 孙回回 | 穆清 | 王淑亚 | 王卫龙 | 马芯宇 | 袁本政 | 赵炳麟 | 焦宇 | 韩传兵 | 张潮洁 | 徐鹏 | 王文青 | 陈正宇 | 安康 | 高翊闵 | 查治国</t>
+          <t>SIMEN ALBINO, ANTON | HEGADE, NARENDRA NARAYANA | DE OLIVEIRA, MURILO | KUMAR, SHUBHAM | FÜCHSEL, GERNOT | SOLANO, ENRIQUE</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>授权专利</t>
+          <t>公开专利</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>本公开的实施例公开了基于计算机视觉的超导量子芯片版图组件自动化识别与提取方法。该方法的一具体实施方式包括：对已读取的超导量子芯片版图进行版图解析，得到组件几何信息集合；对于组件几何信息集合中的每个组件几何信息，根据组件几何信息，生成组件几何信息对应芯片组件的芯片组件图；对得到的芯片组件图集合中的每张芯片组件图进行特征提取，以生成芯片组件图对应的图像描述特征；根据芯片组件图对应的图像描述特征进行芯片组件匹配，以生成芯片组件库。该实施方式显著提升设计效率，减少人工干预。</t>
+          <t>本发明涉及一种计算机实施的方法,用于使用多量子位系统中的数字模拟量子计算(DAQC)操作来解决给定量子硬件的优化问题。</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://analytics.zhihuiya.com/patent-view/abst?patentId=d65a5a52-ea69-41d5-8dfa-c29df156417e&amp;shareId=61CD4199-4E7B-7C36-C999-3CEDB31E0762&amp;from=EXPORT&amp;signature=GVtcBs%2FtkLCC5IRsyGliC9ppoQZ4i7nErCAHJTsvGSM%3D&amp;expire=94608000&amp;date=20260821T055613Z&amp;version=1.0</t>
+          <t>https://analytics.zhihuiya.com/patent-view/abst?patentId=336cd780-97ae-4e13-a91b-0b80f0216285&amp;shareId=F2GF84E7-1GC8-8BEF-B765-D6399653BCG0&amp;from=EXPORT&amp;signature=ZSF6zg6Ya1Kiaee9KP0Y0Z0oqCfmF0uqtxl73AUoJtk%3D&amp;expire=94608000&amp;date=20260828T063351Z&amp;version=1.0</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>波形处理方法、测控系统、量子计算机、介质和设备</t>
+          <t>一种用于逼近一组偏微分方程中至少两个未知变量的计算机实现方法、混合计算系统、计算机程序产品和计算机可读介质</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>本源量子计算科技(合肥)股份有限公司</t>
+          <t>特拉量子股份公司</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>请求不公布姓名 | 孔伟成</t>
+          <t>SAGINGALIEVA, ASEL | MELNIKOV, ALEXEY</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>授权专利</t>
+          <t>公开专利</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>本申请提供了波形处理方法、测控系统、量子计算机、介质和设备，所述方法包括：接收传输波形指令和扫描数据；使用所述扫描数据处理所述传输波形指令，以得到多个输出波形指令；将所述输出波形指令编译成实际波形数据，所述实际波形数据用于在量子计算测控实验任务中对量子比特进行控制或者测量。本申请允许对扫描数据与传输波形指令进行分离传输处理，实现内存的压缩，在编译过程中，所占用的内存较少，能够显著改善内存不足问题，降低任务失败风险，促进量子计算测控实验任务顺利完成，简化波形拼接等操作，允许用户更自由、灵活地去定义实验过程，不仅压缩量子计算测控实验的传输数据量，还有利于解耦实验和硬件，实现跨平台的兼容性。</t>
+          <t>本发明涉及一种计算机实现的、利用量子物理信息神经网络(100)逼近一组偏微分方程的至少两个未知变量(10)的方法,该方法包括以下步骤:提供一个数值网格(20),该网格具有待逼近未知变量(10)的网格坐标(30);提供一个量子物理信息神经网络(100),该量子物理信息神经网络(100)包含一个针对每个未知变量(10)的混合网络(110),其中,各混合网络(110)彼此不互连,每个混合网络(110)具有一个量子网络(120)和一个经典网络(140),其中,该量子网络(120)和该经典网络(140)彼此不互连;将网格坐标 (30) 输入到量子物理信息神经网络 (100) 中,使得网格坐标 (30) 成为每个混合网络 (110) 的输入;并计算每个混合网络 (110) 在每个网格坐标 (30) 处的输出 (Hout),每个输出 (Hout) 对应于网格坐标 (30) 处待近似的不同未知变量 (10),其中每个混合网络 (110) 的输出 (Hout) 是通过组合该混合网络 (110) 的相应量子网络的输出 (Qout) 和相应经典网络的输出 (Cout) 而获得的。本发明还涉及一种混合计算系统、一种计算机程序产品和一种计算机可读介质。</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://analytics.zhihuiya.com/patent-view/abst?patentId=04421a75-2c47-4bb8-ab9e-d0027df4377f&amp;shareId=61CD4199-4E7B-7C36-C999-3CEDB31E0762&amp;from=EXPORT&amp;signature=mfEJLdZgcqEzDdK9HpaO4msJ8LLUIIsEwRdpWbtKue0%3D&amp;expire=94608000&amp;date=20260821T055613Z&amp;version=1.0</t>
+          <t>https://analytics.zhihuiya.com/patent-view/abst?patentId=359ae51c-53a9-4702-bd69-4b2481c42204&amp;shareId=F2GF84E7-1GC8-8BEF-B765-D6399653BCG0&amp;from=EXPORT&amp;signature=FSnWioP6vw5mMY0BjKrxgC790HVsc%2B5%2ByLHmDEquWxE%3D&amp;expire=94608000&amp;date=20260828T063351Z&amp;version=1.0</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>一种量子线路编译方法及相关装置</t>
+          <t>用于量子物体限制器件的混合架构</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>本源量子计算科技(合肥)股份有限公司</t>
+          <t>昆媞努姆有限責任公司</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>窦猛汉 | 请求不公布姓名</t>
+          <t>デイヴィッド·ヘイズ | アレクサンダー·チェルノグゾフ | カーティス·ヴォーリン | ラッセル·ピー·スタッツ | ジョン·パグヌッチ·ゲーブラー | クリストファー·イー·ランガー</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -624,71 +624,71 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>本申请公开了一种量子线路编译方法及相关装置，属于量子计算技术领域，方法包括：将待编译的量子线路的结构与量子芯片的拓扑结构进行匹配，确定目标布局，所确定的目标布局至少使得一个两比特逻辑门作用在相连的物理比特上；确定目标布局对应的所有路由方式；基于由目标路径上量子逻辑门确定的目标分值和目标两比特逻辑门的作用的物理比特之间的距离，对所获得的所有路由方式进行评估，确定目标路由方式；基于所述目标路由方式和对应的目标布局，编译所述量子线路。应用本申请实施例，提高了编译结果的可靠性。</t>
+          <t>本发明提供一种约束装置,其包括一个或多个分选区和一个计算区。每个分选区包括多个分选区射频(RF)导轨,这些导轨限定多个分选约束区域,当施加分选区射频(RD)电压时,这些约束区域用于约束量子物体。每个分选区射频导轨在垂直于其纵轴的方向上具有分选厚度。计算区包括多个计算区射频导轨,这些导轨限定多个计算约束区域,当施加计算区射频电压时,这些约束区域用于约束量子物体。每个计算区射频导轨在垂直于其纵轴的方向上具有计算厚度。计算厚度大于分选厚度。</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://analytics.zhihuiya.com/patent-view/abst?patentId=b22eecb9-0475-4f66-b943-78bbc798537b&amp;shareId=61CD4199-4E7B-7C36-C999-3CEDB31E0762&amp;from=EXPORT&amp;signature=RiVi1gNKx2KqlOAlKXCPJS2GKIxMy402%2FBlDm6o71aU%3D&amp;expire=94608000&amp;date=20260821T055613Z&amp;version=1.0</t>
+          <t>https://analytics.zhihuiya.com/patent-view/abst?patentId=4c357924-dacb-4311-abfc-ff8bf4037b03&amp;shareId=F2GF84E7-1GC8-8BEF-B765-D6399653BCG0&amp;from=EXPORT&amp;signature=zE2W6U0qWjl%2FNp3omIcahGgci3UJF1w9KbJ4Nfo%2Fw8Y%3D&amp;expire=94608000&amp;date=20260828T063351Z&amp;version=1.0</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>一种基于硬件感知的量子任务智能调度系统</t>
+          <t>一种在量子计算机中引入魔态的方法及量子计算机</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>成都中微达信科技有限公司</t>
+          <t>汉阳大学校ERICA产学协力团</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>孟则霖 | 王亚男 | 赵雷 | 冯泠越</t>
+          <t>권영헌 | 김영훈 | 김한솔 | 최원재</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>授权专利</t>
+          <t>公开专利</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>本发明公开了一种基于硬件感知的量子任务智能调度系统，涉及量子技术领域，该系统包括硬件监控模块、特征提取模块、匹配优化模块和调度优化模块；所述硬件监控模块采集物理参数和构建瞬时状态矩阵；所述特征提取模块提取资源特征与噪声特征；所述匹配优化模块最大化计算处理目标量子系统的全局期望成功率；所述调度优化模块基于变化后的瞬时状态矩阵更新全局期望成功率和更新最优任务队列。本发明通过周期性地采集和记录物理量子比特的关键物理参数，并通过动态调整任务队列和实时优化期望成功率，使得量子系统能够根据硬件的实时状态进行调整，从而确保了在任务量和资源需求增加时，提高任务的成功率和系统的整体稳定性。</t>
+          <t>本实施例提供了一种在量子计算机中引入魔态的方法,所述量子计算机中,纠错码包括以下步骤:使用重型六边形结构纠错码配置逻辑量子比特,该纠错码通过在四个数据量子比特和一个伴随式量子比特之间引入两个或多个标志量子比特,从两侧连接两个数据量子比特和一个伴随式量子比特;以及对所述逻辑量子比特执行逻辑运算,其中,所述纠错码执行魔态注入过程,将物理量子比特中实现的魔态映射到逻辑态。</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://analytics.zhihuiya.com/patent-view/abst?patentId=54f19ad3-6630-4ad2-93d7-48ef94ba92ed&amp;shareId=61CD4199-4E7B-7C36-C999-3CEDB31E0762&amp;from=EXPORT&amp;signature=JwQqpOBuJtbdOmaNqcZ%2F0geSU0ba%2FEi8RXVawtNwQV4%3D&amp;expire=94608000&amp;date=20260821T055613Z&amp;version=1.0</t>
+          <t>https://analytics.zhihuiya.com/patent-view/abst?patentId=b6aa7f64-10cc-48f5-a42f-0cd62d4dc3f7&amp;shareId=F2GF84E7-1GC8-8BEF-B765-D6399653BCG0&amp;from=EXPORT&amp;signature=zpNbAJIWG9gU9zRGNcKmQlHmr7nqmVH9UW%2BJ0XnYx6E%3D&amp;expire=94608000&amp;date=20260828T063351Z&amp;version=1.0</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>量子随机数生成速率增强装置及方法</t>
+          <t>一种多比特可扩展量子测控系统</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>合肥国家实验室 | 中国科学技术大学</t>
+          <t>成都中微达信科技有限公司</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>白冰 | 汤晨宇 | 吴佳颖 | 陈瀚深 | 聂友奇 | 刘乃乐 | 蒋一 | 张军 | 潘建伟</t>
+          <t>邹小波 | 林海川 | 曾耿华 | 王渊</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -698,34 +698,34 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>本发明提供了一种量子随机数生成速率增强装置及方法，主要涉及量子信息技术领域。其中，该装置包括：量子熵源模块，用于生成第一量子随机模拟信号；模数转换模块，包括均衡滤波单元；模数转换模块用于：利用均衡滤波单元基于目标幅频响应特征对第一量子随机数字信号的功率谱密度进行平坦化处理，得到经滤波的第一量子随机数字信号；其中，均衡滤波单元加载有滤波系数，以使得均衡滤波单元的目标幅频响应特征与模拟链路的幅频响应特征相反，并使得经滤波的第一量子随机数字信号的信号总能量与初始的第一量子随机数字信号的信号总能量相等；处理模块，用于对经滤波的第一量子随机数字信号进行随机性提取处理，输出量子随机数序列。</t>
+          <t>本发明公开了一种多比特可扩展量子测控系统，在该系统中，量子测控单元、时钟分发单元和触发分发单元均可根据需要测量与控制的量子比特数量进行相应扩展，并通过数据传输网络与上位机进行通信交互，实现量子测控的相关工作；由于量子测控单元的时钟信号和触发信号由时钟分发单元和触发分发单元提供，且时钟分发单元和触发分发由于均是一路输入多路输出，能够通过级联实现大规模的扩展。因此，本发明通过单独地设置时钟分发单元和触发分发单元来为众多的量子测控单元提供时钟信号和触发信号，能够使同步性更加稳定，可提高量子测控的保真度，适用于大规模量子比特扩展的量子测控场景。</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://analytics.zhihuiya.com/patent-view/abst?patentId=965d0b5c-4326-475f-8658-ca0743ae927b&amp;shareId=61CD4199-4E7B-7C36-C999-3CEDB31E0762&amp;from=EXPORT&amp;signature=74ZJa1lm17%2FCCzHp%2F8yP61%2FVLWKUojZ40%2FrM5OqjfkQ%3D&amp;expire=94608000&amp;date=20260821T055613Z&amp;version=1.0</t>
+          <t>https://analytics.zhihuiya.com/patent-view/abst?patentId=70d3a2af-0890-42d6-871b-abd15755d8e3&amp;shareId=F2GF84E7-1GC8-8BEF-B765-D6399653BCG0&amp;from=EXPORT&amp;signature=nM5DGXzZRDvLt6JnuiRFRvUPULFErzi3Oeg3JQBN6q0%3D&amp;expire=94608000&amp;date=20260828T063351Z&amp;version=1.0</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>光子的频域任意线性变换</t>
+          <t>经典增强变分量子本征求解器</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>利兰斯坦福初级大学董事会</t>
+          <t>札帕塔运算股份有限公司</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>BUDDHIRAJU, SIDDHARTH | DUTT, AVIK | MINKOV, MOMCHIL | WILLIAMSON, IAN A.D. | FAN, SHANHUI</t>
+          <t>RADIN, MAXWELL D. | JOHNSON, PETER D.</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -735,17 +735,17 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>一个或多个光学谐振器依次耦合到光波导上。每个谐振器都包含一个相应的调制器。信号控制器配置为使用相应的复合电信号驱动每个调制器。每个复合电信号包含由一个或多个谐振器定义的频率梳的两个或多个频率分量。这种配置的结果是,波导输入端和输出端之间的输入输出关系是由复合电信号定义的线性变换,该线性变换以频率梳的频率为基。这种线性变换可以是互易的或非互易的,也可以是酉变换或非酉变换。</t>
+          <t>本发明提供了一种利用经典增强型变分量子本征求解器(VQE)估计费米子哈密顿量基态和激发态能量的方法和系统。所公开的技术克服了先前VQE方法的缺点,即需要大量的电路重复和过长的运行时间才能达到精度,尤其是在使用噪声中等规模量子(NISQ)器件实现时。本发明公开的经典增强型VQE利用经典方法估计期望值。量子计算机无需制备试探态,而是利用试探态与目标态的经典可处理近似之间的差异。基态能量估计速度显著提高。此外,仅使用基态与用于增强的计算基态之间的重叠,即可估计传统VQE单基态增强的测量减少量。</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://analytics.zhihuiya.com/patent-view/abst?patentId=eca76b41-9d2c-4c94-948c-fb1fb17da9dc&amp;shareId=61CD4199-4E7B-7C36-C999-3CEDB31E0762&amp;from=EXPORT&amp;signature=XPsNTOwpGZQ%2B9lmVGiWB5k4UNsx5zbBCj16vGadREf4%3D&amp;expire=94608000&amp;date=20260821T055613Z&amp;version=1.0</t>
+          <t>https://analytics.zhihuiya.com/patent-view/abst?patentId=e62d8def-1623-4b88-9dec-9d2da97fb7be&amp;shareId=F2GF84E7-1GC8-8BEF-B765-D6399653BCG0&amp;from=EXPORT&amp;signature=iDg0nvUQBsy0eTiVqkGwrTIighDJymPw0S%2Bvx%2BbK63M%3D&amp;expire=94608000&amp;date=20260828T063351Z&amp;version=1.0</t>
         </is>
       </c>
     </row>
